--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125587992</v>
+        <v>125591515</v>
       </c>
       <c r="B2" t="n">
-        <v>8436</v>
+        <v>91792</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617331</v>
+        <v>617222</v>
       </c>
       <c r="R2" t="n">
-        <v>6562828</v>
+        <v>6562777</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125589789</v>
+        <v>125587649</v>
       </c>
       <c r="B3" t="n">
-        <v>96522</v>
+        <v>8436</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617001</v>
+        <v>617157</v>
       </c>
       <c r="R3" t="n">
-        <v>6562435</v>
+        <v>6562656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125587441</v>
+        <v>125588919</v>
       </c>
       <c r="B4" t="n">
-        <v>8436</v>
+        <v>97150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617045</v>
+        <v>617195</v>
       </c>
       <c r="R4" t="n">
-        <v>6562557</v>
+        <v>6562875</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125587649</v>
+        <v>125588214</v>
       </c>
       <c r="B5" t="n">
-        <v>8436</v>
+        <v>96522</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,43 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617157</v>
+        <v>617309</v>
       </c>
       <c r="R5" t="n">
-        <v>6562656</v>
+        <v>6562860</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125589723</v>
+        <v>125588011</v>
       </c>
       <c r="B6" t="n">
-        <v>96522</v>
+        <v>97147</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,38 +1100,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>617043</v>
+        <v>617337</v>
       </c>
       <c r="R6" t="n">
-        <v>6562446</v>
+        <v>6562838</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125588919</v>
+        <v>125587620</v>
       </c>
       <c r="B7" t="n">
-        <v>97150</v>
+        <v>95719</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,34 +1206,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>617195</v>
+        <v>617137</v>
       </c>
       <c r="R7" t="n">
-        <v>6562875</v>
+        <v>6562634</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125589867</v>
+        <v>125589789</v>
       </c>
       <c r="B8" t="n">
-        <v>91186</v>
+        <v>96522</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,43 +1317,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616990</v>
+        <v>617001</v>
       </c>
       <c r="R8" t="n">
-        <v>6562418</v>
+        <v>6562435</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1403,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125589579</v>
+        <v>125588805</v>
       </c>
       <c r="B9" t="n">
         <v>8436</v>
@@ -1447,21 +1437,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>617116</v>
+        <v>617207</v>
       </c>
       <c r="R9" t="n">
-        <v>6562497</v>
+        <v>6562981</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125588011</v>
+        <v>125587992</v>
       </c>
       <c r="B10" t="n">
-        <v>97147</v>
+        <v>8436</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,34 +1521,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>617337</v>
+        <v>617331</v>
       </c>
       <c r="R10" t="n">
-        <v>6562838</v>
+        <v>6562828</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125587620</v>
+        <v>125589867</v>
       </c>
       <c r="B11" t="n">
-        <v>95719</v>
+        <v>91186</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,25 +1624,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1662,19 +1652,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>617137</v>
+        <v>616990</v>
       </c>
       <c r="R11" t="n">
-        <v>6562634</v>
+        <v>6562418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125588127</v>
+        <v>125587385</v>
       </c>
       <c r="B12" t="n">
-        <v>57648</v>
+        <v>5196</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1745,20 +1735,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100048</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1766,26 +1756,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>617343</v>
+        <v>617059</v>
       </c>
       <c r="R12" t="n">
-        <v>6562872</v>
+        <v>6562493</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,19 +1801,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>07:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1854,7 +1830,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125587652</v>
+        <v>125589579</v>
       </c>
       <c r="B13" t="n">
         <v>8436</v>
@@ -1895,14 +1871,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>617165</v>
+        <v>617116</v>
       </c>
       <c r="R13" t="n">
-        <v>6562682</v>
+        <v>6562497</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,10 +1937,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125588214</v>
+        <v>125587652</v>
       </c>
       <c r="B14" t="n">
-        <v>96522</v>
+        <v>8436</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,38 +1949,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>617309</v>
+        <v>617165</v>
       </c>
       <c r="R14" t="n">
-        <v>6562860</v>
+        <v>6562682</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,10 +2044,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125587385</v>
+        <v>125588127</v>
       </c>
       <c r="B15" t="n">
-        <v>5196</v>
+        <v>57648</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2075,20 +2056,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>100048</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2096,22 +2077,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>617059</v>
+        <v>617343</v>
       </c>
       <c r="R15" t="n">
-        <v>6562493</v>
+        <v>6562872</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,9 +2126,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>07:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2170,10 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125588805</v>
+        <v>125589723</v>
       </c>
       <c r="B16" t="n">
-        <v>8436</v>
+        <v>96522</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2182,38 +2177,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>617207</v>
+        <v>617043</v>
       </c>
       <c r="R16" t="n">
-        <v>6562981</v>
+        <v>6562446</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2272,10 +2267,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125591515</v>
+        <v>125587441</v>
       </c>
       <c r="B17" t="n">
-        <v>91792</v>
+        <v>8436</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2288,37 +2283,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>617222</v>
+        <v>617045</v>
       </c>
       <c r="R17" t="n">
-        <v>6562777</v>
+        <v>6562557</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125591515</v>
+        <v>125588127</v>
       </c>
       <c r="B2" t="n">
-        <v>91792</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57664</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617222</v>
+        <v>617343</v>
       </c>
       <c r="R2" t="n">
-        <v>6562777</v>
+        <v>6562872</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +752,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>07:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125587649</v>
+        <v>125587385</v>
       </c>
       <c r="B3" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617157</v>
+        <v>617059</v>
       </c>
       <c r="R3" t="n">
-        <v>6562656</v>
+        <v>6562493</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,12 +896,7 @@
         <v>125588919</v>
       </c>
       <c r="B4" t="n">
-        <v>97150</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125588214</v>
+        <v>125589789</v>
       </c>
       <c r="B5" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,14 +1021,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617309</v>
+        <v>617001</v>
       </c>
       <c r="R5" t="n">
-        <v>6562860</v>
+        <v>6562435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,15 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125588011</v>
+        <v>125587649</v>
       </c>
       <c r="B6" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,34 +1098,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>617337</v>
+        <v>617157</v>
       </c>
       <c r="R6" t="n">
-        <v>6562838</v>
+        <v>6562656</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,37 +1189,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125587620</v>
+        <v>125589867</v>
       </c>
       <c r="B7" t="n">
-        <v>95719</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91240</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1230,19 +1224,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>617137</v>
+        <v>616990</v>
       </c>
       <c r="R7" t="n">
-        <v>6562634</v>
+        <v>6562418</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,50 +1295,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125589789</v>
+        <v>125589579</v>
       </c>
       <c r="B8" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>617001</v>
+        <v>617116</v>
       </c>
       <c r="R8" t="n">
-        <v>6562435</v>
+        <v>6562497</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,16 +1397,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125588805</v>
+        <v>125587652</v>
       </c>
       <c r="B9" t="n">
         <v>8436</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1437,16 +1426,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>617207</v>
+        <v>617165</v>
       </c>
       <c r="R9" t="n">
-        <v>6562981</v>
+        <v>6562682</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,16 +1499,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125587992</v>
+        <v>125588805</v>
       </c>
       <c r="B10" t="n">
         <v>8436</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1539,21 +1528,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>617331</v>
+        <v>617207</v>
       </c>
       <c r="R10" t="n">
-        <v>6562828</v>
+        <v>6562981</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,59 +1596,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125589867</v>
+        <v>125588011</v>
       </c>
       <c r="B11" t="n">
-        <v>91186</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616990</v>
+        <v>617337</v>
       </c>
       <c r="R11" t="n">
-        <v>6562418</v>
+        <v>6562838</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,15 +1693,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125587385</v>
+        <v>125587441</v>
       </c>
       <c r="B12" t="n">
-        <v>5196</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,21 +1704,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1768,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>617059</v>
+        <v>617045</v>
       </c>
       <c r="R12" t="n">
-        <v>6562493</v>
+        <v>6562557</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,15 +1795,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125589579</v>
+        <v>125587620</v>
       </c>
       <c r="B13" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95773</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,27 +1806,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>210</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1875,10 +1839,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>617116</v>
+        <v>617137</v>
       </c>
       <c r="R13" t="n">
-        <v>6562497</v>
+        <v>6562634</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,16 +1901,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125587652</v>
+        <v>125587992</v>
       </c>
       <c r="B14" t="n">
         <v>8436</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1973,7 +1932,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1982,10 +1941,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>617165</v>
+        <v>617331</v>
       </c>
       <c r="R14" t="n">
-        <v>6562682</v>
+        <v>6562828</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,62 +2003,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125588127</v>
+        <v>125591515</v>
       </c>
       <c r="B15" t="n">
-        <v>57648</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100048</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>617343</v>
+        <v>617222</v>
       </c>
       <c r="R15" t="n">
-        <v>6562872</v>
+        <v>6562777</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2126,19 +2071,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>07:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,12 +2103,7 @@
         <v>125589723</v>
       </c>
       <c r="B16" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,55 +2197,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125587441</v>
+        <v>125588214</v>
       </c>
       <c r="B17" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>617045</v>
+        <v>617309</v>
       </c>
       <c r="R17" t="n">
-        <v>6562557</v>
+        <v>6562860</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,6 +2291,2597 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125898903</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>616923</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6562795</v>
+      </c>
+      <c r="S18" t="n">
+        <v>141</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125898809</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91240</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>617125</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6562956</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125897482</v>
+      </c>
+      <c r="B20" t="n">
+        <v>96577</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>53</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>617058</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6562436</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125897879</v>
+      </c>
+      <c r="B21" t="n">
+        <v>96577</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>53</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>617120</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6562558</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125898363</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91220</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Svartkärret, Svartkärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>617347</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6562816</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125898834</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91240</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>617150</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6562910</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125897268</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8436</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Dammkärr, Dammkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>617001</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6562375</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125898191</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96577</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>53</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>617135</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6562631</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125899099</v>
+      </c>
+      <c r="B26" t="n">
+        <v>8436</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>616903</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6562497</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125898277</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Svartkärret, Svartkärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>617391</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6562762</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125898383</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58019</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svartkärret, Svartkärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>617351</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6562821</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125898677</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8436</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Penningdroget, Penningdroget, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>617387</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6562949</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125898500</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98241</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Svartkärret, Svartkärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>617391</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6562882</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125897235</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91240</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Dammkärr, Dammkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>616952</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6562293</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125897176</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Dammkärr, Dammkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>616909</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6562353</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125898782</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8436</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Penningdroget, Penningdroget, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>617277</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6562986</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125897659</v>
+      </c>
+      <c r="B34" t="n">
+        <v>96577</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>53</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>617082</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6562457</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125897142</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57809</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Dammkärr, Dammkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>616889</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6562374</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125898732</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Penningdroget, Penningdroget, Srm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>617358</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6562976</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125899125</v>
+      </c>
+      <c r="B37" t="n">
+        <v>8436</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>616870</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6562497</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125898796</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8436</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Penningdroget, Penningdroget, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>617250</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6562964</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125898857</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>617020</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6562779</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125898693</v>
+      </c>
+      <c r="B40" t="n">
+        <v>8436</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Penningdroget, Penningdroget, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>617374</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6562974</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125898612</v>
+      </c>
+      <c r="B41" t="n">
+        <v>105348</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Svartkärret, Svartkärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>617388</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6562892</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125897532</v>
+      </c>
+      <c r="B42" t="n">
+        <v>96577</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>53</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>617072</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6562443</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125587385</v>
+        <v>125588919</v>
       </c>
       <c r="B3" t="n">
-        <v>5196</v>
+        <v>97205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,39 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617059</v>
+        <v>617195</v>
       </c>
       <c r="R3" t="n">
-        <v>6562493</v>
+        <v>6562875</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125588919</v>
+        <v>125587385</v>
       </c>
       <c r="B4" t="n">
-        <v>97205</v>
+        <v>5196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,34 +899,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617195</v>
+        <v>617059</v>
       </c>
       <c r="R4" t="n">
-        <v>6562875</v>
+        <v>6562493</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -4472,50 +4472,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125898857</v>
+        <v>125898693</v>
       </c>
       <c r="B39" t="n">
-        <v>57648</v>
+        <v>8436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617020</v>
+        <v>617374</v>
       </c>
       <c r="R39" t="n">
-        <v>6562779</v>
+        <v>6562974</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4545,19 +4545,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,50 +4574,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125898693</v>
+        <v>125898857</v>
       </c>
       <c r="B40" t="n">
-        <v>8436</v>
+        <v>57648</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617374</v>
+        <v>617020</v>
       </c>
       <c r="R40" t="n">
-        <v>6562974</v>
+        <v>6562779</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4657,9 +4647,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125588919</v>
+        <v>125587385</v>
       </c>
       <c r="B3" t="n">
-        <v>97205</v>
+        <v>5196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +802,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617195</v>
+        <v>617059</v>
       </c>
       <c r="R3" t="n">
-        <v>6562875</v>
+        <v>6562493</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125587385</v>
+        <v>125588919</v>
       </c>
       <c r="B4" t="n">
-        <v>5196</v>
+        <v>97212</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,39 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617059</v>
+        <v>617195</v>
       </c>
       <c r="R4" t="n">
-        <v>6562493</v>
+        <v>6562875</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
         <v>125589789</v>
       </c>
       <c r="B5" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>125589867</v>
       </c>
       <c r="B7" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>125588011</v>
       </c>
       <c r="B11" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>125587620</v>
       </c>
       <c r="B13" t="n">
-        <v>95773</v>
+        <v>95780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,48 +2003,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125591515</v>
+        <v>125589723</v>
       </c>
       <c r="B15" t="n">
-        <v>91846</v>
+        <v>96584</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>617222</v>
+        <v>617043</v>
       </c>
       <c r="R15" t="n">
-        <v>6562777</v>
+        <v>6562446</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2100,48 +2100,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125589723</v>
+        <v>125591515</v>
       </c>
       <c r="B16" t="n">
-        <v>96577</v>
+        <v>91853</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>617043</v>
+        <v>617222</v>
       </c>
       <c r="R16" t="n">
-        <v>6562446</v>
+        <v>6562777</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>125588214</v>
       </c>
       <c r="B17" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125898903</v>
+        <v>125898809</v>
       </c>
       <c r="B18" t="n">
-        <v>57648</v>
+        <v>91247</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,42 +2305,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bobesök?</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616923</v>
+        <v>617125</v>
       </c>
       <c r="R18" t="n">
-        <v>6562795</v>
+        <v>6562956</v>
       </c>
       <c r="S18" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2367,19 +2371,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,10 +2400,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125898809</v>
+        <v>125898903</v>
       </c>
       <c r="B19" t="n">
-        <v>91240</v>
+        <v>57648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2417,46 +2411,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>617125</v>
+        <v>616923</v>
       </c>
       <c r="R19" t="n">
-        <v>6562956</v>
+        <v>6562795</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2483,9 +2473,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2515,7 +2515,7 @@
         <v>125897482</v>
       </c>
       <c r="B20" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,45 +2609,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125897879</v>
+        <v>125897268</v>
       </c>
       <c r="B21" t="n">
-        <v>96577</v>
+        <v>8436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617120</v>
+        <v>617001</v>
       </c>
       <c r="R21" t="n">
-        <v>6562558</v>
+        <v>6562375</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2709,7 +2714,7 @@
         <v>125898363</v>
       </c>
       <c r="B22" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2803,10 +2808,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125898834</v>
+        <v>125897879</v>
       </c>
       <c r="B23" t="n">
-        <v>91240</v>
+        <v>96584</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2814,43 +2819,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617150</v>
+        <v>617120</v>
       </c>
       <c r="R23" t="n">
-        <v>6562910</v>
+        <v>6562558</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2909,50 +2905,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125897268</v>
+        <v>125898834</v>
       </c>
       <c r="B24" t="n">
-        <v>8436</v>
+        <v>91247</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617001</v>
+        <v>617150</v>
       </c>
       <c r="R24" t="n">
-        <v>6562375</v>
+        <v>6562910</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3011,45 +3011,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125898191</v>
+        <v>125899099</v>
       </c>
       <c r="B25" t="n">
-        <v>96577</v>
+        <v>8436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>617135</v>
+        <v>616903</v>
       </c>
       <c r="R25" t="n">
-        <v>6562631</v>
+        <v>6562497</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,50 +3113,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125899099</v>
+        <v>125898191</v>
       </c>
       <c r="B26" t="n">
-        <v>8436</v>
+        <v>96584</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>616903</v>
+        <v>617135</v>
       </c>
       <c r="R26" t="n">
-        <v>6562497</v>
+        <v>6562631</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3429,50 +3429,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125898677</v>
+        <v>125897235</v>
       </c>
       <c r="B29" t="n">
-        <v>8436</v>
+        <v>91247</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>617387</v>
+        <v>616952</v>
       </c>
       <c r="R29" t="n">
-        <v>6562949</v>
+        <v>6562293</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3535,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125898500</v>
+        <v>125898677</v>
       </c>
       <c r="B30" t="n">
-        <v>98241</v>
+        <v>8436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3542,34 +3546,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617391</v>
+        <v>617387</v>
       </c>
       <c r="R30" t="n">
-        <v>6562882</v>
+        <v>6562949</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3628,54 +3637,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125897235</v>
+        <v>125898500</v>
       </c>
       <c r="B31" t="n">
-        <v>91240</v>
+        <v>98248</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>616952</v>
+        <v>617391</v>
       </c>
       <c r="R31" t="n">
-        <v>6562293</v>
+        <v>6562882</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3941,7 +3941,7 @@
         <v>125897659</v>
       </c>
       <c r="B34" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125897142</v>
+        <v>125898732</v>
       </c>
       <c r="B35" t="n">
-        <v>57809</v>
+        <v>57648</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4046,16 +4046,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4063,31 +4063,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>616889</v>
+        <v>617358</v>
       </c>
       <c r="R35" t="n">
-        <v>6562374</v>
+        <v>6562976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4119,7 +4110,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4129,7 +4120,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4156,10 +4147,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125898732</v>
+        <v>125897142</v>
       </c>
       <c r="B36" t="n">
-        <v>57648</v>
+        <v>57809</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4167,16 +4158,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4184,22 +4175,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617358</v>
+        <v>616889</v>
       </c>
       <c r="R36" t="n">
-        <v>6562976</v>
+        <v>6562374</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4472,50 +4472,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125898693</v>
+        <v>125898857</v>
       </c>
       <c r="B39" t="n">
-        <v>8436</v>
+        <v>57648</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617374</v>
+        <v>617020</v>
       </c>
       <c r="R39" t="n">
-        <v>6562974</v>
+        <v>6562779</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4545,9 +4545,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4574,50 +4584,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125898857</v>
+        <v>125898693</v>
       </c>
       <c r="B40" t="n">
-        <v>57648</v>
+        <v>8436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617020</v>
+        <v>617374</v>
       </c>
       <c r="R40" t="n">
-        <v>6562779</v>
+        <v>6562974</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4647,19 +4657,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4689,7 +4689,7 @@
         <v>125898612</v>
       </c>
       <c r="B41" t="n">
-        <v>105348</v>
+        <v>105355</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>125897532</v>
       </c>
       <c r="B42" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -2294,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125898809</v>
+        <v>125898903</v>
       </c>
       <c r="B18" t="n">
-        <v>91247</v>
+        <v>57648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,46 +2305,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>617125</v>
+        <v>616923</v>
       </c>
       <c r="R18" t="n">
-        <v>6562956</v>
+        <v>6562795</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2371,9 +2367,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2400,10 +2406,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125898903</v>
+        <v>125898809</v>
       </c>
       <c r="B19" t="n">
-        <v>57648</v>
+        <v>91247</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2411,42 +2417,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>bobesök?</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616923</v>
+        <v>617125</v>
       </c>
       <c r="R19" t="n">
-        <v>6562795</v>
+        <v>6562956</v>
       </c>
       <c r="S19" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2473,19 +2483,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,50 +2609,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125897268</v>
+        <v>125897879</v>
       </c>
       <c r="B21" t="n">
-        <v>8436</v>
+        <v>96584</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617001</v>
+        <v>617120</v>
       </c>
       <c r="R21" t="n">
-        <v>6562375</v>
+        <v>6562558</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2808,10 +2803,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125897879</v>
+        <v>125898834</v>
       </c>
       <c r="B23" t="n">
-        <v>96584</v>
+        <v>91247</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2819,34 +2814,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617120</v>
+        <v>617150</v>
       </c>
       <c r="R23" t="n">
-        <v>6562558</v>
+        <v>6562910</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2905,54 +2909,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125898834</v>
+        <v>125897268</v>
       </c>
       <c r="B24" t="n">
-        <v>91247</v>
+        <v>8436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617150</v>
+        <v>617001</v>
       </c>
       <c r="R24" t="n">
-        <v>6562910</v>
+        <v>6562375</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3429,54 +3429,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125897235</v>
+        <v>125898500</v>
       </c>
       <c r="B29" t="n">
-        <v>91247</v>
+        <v>98248</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>616952</v>
+        <v>617391</v>
       </c>
       <c r="R29" t="n">
-        <v>6562293</v>
+        <v>6562882</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3535,50 +3526,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125898677</v>
+        <v>125897235</v>
       </c>
       <c r="B30" t="n">
-        <v>8436</v>
+        <v>91247</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617387</v>
+        <v>616952</v>
       </c>
       <c r="R30" t="n">
-        <v>6562949</v>
+        <v>6562293</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3637,10 +3632,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125898500</v>
+        <v>125898677</v>
       </c>
       <c r="B31" t="n">
-        <v>98248</v>
+        <v>8436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3648,34 +3643,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>617391</v>
+        <v>617387</v>
       </c>
       <c r="R31" t="n">
-        <v>6562882</v>
+        <v>6562949</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -2409,7 +2409,7 @@
         <v>125898809</v>
       </c>
       <c r="B19" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>125897482</v>
       </c>
       <c r="B20" t="n">
-        <v>96584</v>
+        <v>96585</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125897879</v>
+        <v>125898834</v>
       </c>
       <c r="B21" t="n">
-        <v>96584</v>
+        <v>91248</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,34 +2620,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617120</v>
+        <v>617150</v>
       </c>
       <c r="R21" t="n">
-        <v>6562558</v>
+        <v>6562910</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,45 +2715,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125898363</v>
+        <v>125897268</v>
       </c>
       <c r="B22" t="n">
-        <v>91227</v>
+        <v>8436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617347</v>
+        <v>617001</v>
       </c>
       <c r="R22" t="n">
-        <v>6562816</v>
+        <v>6562375</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2803,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125898834</v>
+        <v>125897879</v>
       </c>
       <c r="B23" t="n">
-        <v>91247</v>
+        <v>96585</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2814,43 +2828,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617150</v>
+        <v>617120</v>
       </c>
       <c r="R23" t="n">
-        <v>6562910</v>
+        <v>6562558</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2909,50 +2914,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125897268</v>
+        <v>125898363</v>
       </c>
       <c r="B24" t="n">
-        <v>8436</v>
+        <v>91228</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617001</v>
+        <v>617347</v>
       </c>
       <c r="R24" t="n">
-        <v>6562375</v>
+        <v>6562816</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3011,50 +3011,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125899099</v>
+        <v>125898191</v>
       </c>
       <c r="B25" t="n">
-        <v>8436</v>
+        <v>96585</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>616903</v>
+        <v>617135</v>
       </c>
       <c r="R25" t="n">
-        <v>6562497</v>
+        <v>6562631</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3113,45 +3108,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125898191</v>
+        <v>125899099</v>
       </c>
       <c r="B26" t="n">
-        <v>96584</v>
+        <v>8436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>617135</v>
+        <v>616903</v>
       </c>
       <c r="R26" t="n">
-        <v>6562631</v>
+        <v>6562497</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,7 +3325,7 @@
         <v>125898383</v>
       </c>
       <c r="B28" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3429,45 +3429,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125898500</v>
+        <v>125897235</v>
       </c>
       <c r="B29" t="n">
-        <v>98248</v>
+        <v>91248</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>617391</v>
+        <v>616952</v>
       </c>
       <c r="R29" t="n">
-        <v>6562882</v>
+        <v>6562293</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3526,54 +3535,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125897235</v>
+        <v>125898677</v>
       </c>
       <c r="B30" t="n">
-        <v>91247</v>
+        <v>8436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>616952</v>
+        <v>617387</v>
       </c>
       <c r="R30" t="n">
-        <v>6562293</v>
+        <v>6562949</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,10 +3637,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125898677</v>
+        <v>125898500</v>
       </c>
       <c r="B31" t="n">
-        <v>8436</v>
+        <v>98249</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,39 +3648,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106554</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>617387</v>
+        <v>617391</v>
       </c>
       <c r="R31" t="n">
-        <v>6562949</v>
+        <v>6562882</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3941,7 +3941,7 @@
         <v>125897659</v>
       </c>
       <c r="B34" t="n">
-        <v>96584</v>
+        <v>96585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4147,59 +4147,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125897142</v>
+        <v>125899125</v>
       </c>
       <c r="B36" t="n">
-        <v>57809</v>
+        <v>8436</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>616889</v>
+        <v>616870</v>
       </c>
       <c r="R36" t="n">
-        <v>6562374</v>
+        <v>6562497</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4229,19 +4220,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>07:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4268,50 +4249,59 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125899125</v>
+        <v>125897142</v>
       </c>
       <c r="B37" t="n">
-        <v>8436</v>
+        <v>57809</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106554</v>
+        <v>103020</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616870</v>
+        <v>616889</v>
       </c>
       <c r="R37" t="n">
-        <v>6562497</v>
+        <v>6562374</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4341,9 +4331,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4689,7 +4689,7 @@
         <v>125898612</v>
       </c>
       <c r="B41" t="n">
-        <v>105355</v>
+        <v>105356</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>125897532</v>
       </c>
       <c r="B42" t="n">
-        <v>96584</v>
+        <v>96585</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125587385</v>
+        <v>125588919</v>
       </c>
       <c r="B3" t="n">
-        <v>5196</v>
+        <v>97215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,39 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617059</v>
+        <v>617195</v>
       </c>
       <c r="R3" t="n">
-        <v>6562493</v>
+        <v>6562875</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125588919</v>
+        <v>125587385</v>
       </c>
       <c r="B4" t="n">
-        <v>97212</v>
+        <v>5196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,34 +899,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617195</v>
+        <v>617059</v>
       </c>
       <c r="R4" t="n">
-        <v>6562875</v>
+        <v>6562493</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
         <v>125589789</v>
       </c>
       <c r="B5" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>125589867</v>
       </c>
       <c r="B7" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>125588011</v>
       </c>
       <c r="B11" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>125587620</v>
       </c>
       <c r="B13" t="n">
-        <v>95780</v>
+        <v>95783</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>125589723</v>
       </c>
       <c r="B15" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>125591515</v>
       </c>
       <c r="B16" t="n">
-        <v>91853</v>
+        <v>91857</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>125588214</v>
       </c>
       <c r="B17" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125898903</v>
+        <v>125898809</v>
       </c>
       <c r="B18" t="n">
-        <v>57648</v>
+        <v>91248</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,42 +2305,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bobesök?</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616923</v>
+        <v>617125</v>
       </c>
       <c r="R18" t="n">
-        <v>6562795</v>
+        <v>6562956</v>
       </c>
       <c r="S18" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2367,19 +2371,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,10 +2400,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125898809</v>
+        <v>125898903</v>
       </c>
       <c r="B19" t="n">
-        <v>91248</v>
+        <v>57648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2417,46 +2411,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>617125</v>
+        <v>616923</v>
       </c>
       <c r="R19" t="n">
-        <v>6562956</v>
+        <v>6562795</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2483,9 +2473,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2515,7 +2515,7 @@
         <v>125897482</v>
       </c>
       <c r="B20" t="n">
-        <v>96585</v>
+        <v>96587</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125898834</v>
+        <v>125897879</v>
       </c>
       <c r="B21" t="n">
-        <v>91248</v>
+        <v>96587</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,43 +2620,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617150</v>
+        <v>617120</v>
       </c>
       <c r="R21" t="n">
-        <v>6562910</v>
+        <v>6562558</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,50 +2706,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125897268</v>
+        <v>125898834</v>
       </c>
       <c r="B22" t="n">
-        <v>8436</v>
+        <v>91248</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617001</v>
+        <v>617150</v>
       </c>
       <c r="R22" t="n">
-        <v>6562375</v>
+        <v>6562910</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2812,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125897879</v>
+        <v>125898363</v>
       </c>
       <c r="B23" t="n">
-        <v>96585</v>
+        <v>91228</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,34 +2823,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617120</v>
+        <v>617347</v>
       </c>
       <c r="R23" t="n">
-        <v>6562558</v>
+        <v>6562816</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2914,45 +2909,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125898363</v>
+        <v>125897268</v>
       </c>
       <c r="B24" t="n">
-        <v>91228</v>
+        <v>8436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617347</v>
+        <v>617001</v>
       </c>
       <c r="R24" t="n">
-        <v>6562816</v>
+        <v>6562375</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
         <v>125898191</v>
       </c>
       <c r="B25" t="n">
-        <v>96585</v>
+        <v>96587</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>125898500</v>
       </c>
       <c r="B31" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>125897659</v>
       </c>
       <c r="B34" t="n">
-        <v>96585</v>
+        <v>96587</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4472,50 +4472,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125898857</v>
+        <v>125898693</v>
       </c>
       <c r="B39" t="n">
-        <v>57648</v>
+        <v>8436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617020</v>
+        <v>617374</v>
       </c>
       <c r="R39" t="n">
-        <v>6562779</v>
+        <v>6562974</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4545,19 +4545,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,50 +4574,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125898693</v>
+        <v>125898857</v>
       </c>
       <c r="B40" t="n">
-        <v>8436</v>
+        <v>57648</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617374</v>
+        <v>617020</v>
       </c>
       <c r="R40" t="n">
-        <v>6562974</v>
+        <v>6562779</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4657,9 +4647,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4689,7 +4689,7 @@
         <v>125898612</v>
       </c>
       <c r="B41" t="n">
-        <v>105356</v>
+        <v>105358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>125897532</v>
       </c>
       <c r="B42" t="n">
-        <v>96585</v>
+        <v>96587</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125588919</v>
+        <v>125587385</v>
       </c>
       <c r="B3" t="n">
-        <v>97215</v>
+        <v>5196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +802,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617195</v>
+        <v>617059</v>
       </c>
       <c r="R3" t="n">
-        <v>6562875</v>
+        <v>6562493</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125587385</v>
+        <v>125588919</v>
       </c>
       <c r="B4" t="n">
-        <v>5196</v>
+        <v>97215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,39 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617059</v>
+        <v>617195</v>
       </c>
       <c r="R4" t="n">
-        <v>6562493</v>
+        <v>6562875</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125588919</v>
       </c>
       <c r="B4" t="n">
-        <v>97215</v>
+        <v>97219</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>125589789</v>
       </c>
       <c r="B5" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>125589867</v>
       </c>
       <c r="B7" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>125588011</v>
       </c>
       <c r="B11" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>125587620</v>
       </c>
       <c r="B13" t="n">
-        <v>95783</v>
+        <v>95787</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>125589723</v>
       </c>
       <c r="B15" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>125591515</v>
       </c>
       <c r="B16" t="n">
-        <v>91857</v>
+        <v>91861</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>125588214</v>
       </c>
       <c r="B17" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>125898809</v>
       </c>
       <c r="B18" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>125897482</v>
       </c>
       <c r="B20" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125897879</v>
+        <v>125898363</v>
       </c>
       <c r="B21" t="n">
-        <v>96587</v>
+        <v>91232</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,34 +2620,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617120</v>
+        <v>617347</v>
       </c>
       <c r="R21" t="n">
-        <v>6562558</v>
+        <v>6562816</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2709,7 +2709,7 @@
         <v>125898834</v>
       </c>
       <c r="B22" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2812,10 +2812,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125898363</v>
+        <v>125897879</v>
       </c>
       <c r="B23" t="n">
-        <v>91228</v>
+        <v>96591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2823,34 +2823,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617347</v>
+        <v>617120</v>
       </c>
       <c r="R23" t="n">
-        <v>6562816</v>
+        <v>6562558</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3011,45 +3011,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125898191</v>
+        <v>125899099</v>
       </c>
       <c r="B25" t="n">
-        <v>96587</v>
+        <v>8436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>617135</v>
+        <v>616903</v>
       </c>
       <c r="R25" t="n">
-        <v>6562631</v>
+        <v>6562497</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,50 +3113,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125899099</v>
+        <v>125898191</v>
       </c>
       <c r="B26" t="n">
-        <v>8436</v>
+        <v>96591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>616903</v>
+        <v>617135</v>
       </c>
       <c r="R26" t="n">
-        <v>6562497</v>
+        <v>6562631</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3432,7 +3432,7 @@
         <v>125897235</v>
       </c>
       <c r="B29" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>125898500</v>
       </c>
       <c r="B31" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>125897659</v>
       </c>
       <c r="B34" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125898732</v>
+        <v>125897142</v>
       </c>
       <c r="B35" t="n">
-        <v>57648</v>
+        <v>57809</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4046,16 +4046,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4063,22 +4063,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>617358</v>
+        <v>616889</v>
       </c>
       <c r="R35" t="n">
-        <v>6562976</v>
+        <v>6562374</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4110,7 +4119,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4120,7 +4129,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4147,50 +4156,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125899125</v>
+        <v>125898732</v>
       </c>
       <c r="B36" t="n">
-        <v>8436</v>
+        <v>57648</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>616870</v>
+        <v>617358</v>
       </c>
       <c r="R36" t="n">
-        <v>6562497</v>
+        <v>6562976</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4220,9 +4229,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4249,59 +4268,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125897142</v>
+        <v>125899125</v>
       </c>
       <c r="B37" t="n">
-        <v>57809</v>
+        <v>8436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616889</v>
+        <v>616870</v>
       </c>
       <c r="R37" t="n">
-        <v>6562374</v>
+        <v>6562497</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4331,19 +4341,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>07:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4472,50 +4472,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125898693</v>
+        <v>125898857</v>
       </c>
       <c r="B39" t="n">
-        <v>8436</v>
+        <v>57648</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617374</v>
+        <v>617020</v>
       </c>
       <c r="R39" t="n">
-        <v>6562974</v>
+        <v>6562779</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4545,9 +4545,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4574,50 +4584,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125898857</v>
+        <v>125898693</v>
       </c>
       <c r="B40" t="n">
-        <v>57648</v>
+        <v>8436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617020</v>
+        <v>617374</v>
       </c>
       <c r="R40" t="n">
-        <v>6562779</v>
+        <v>6562974</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4647,19 +4657,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4689,7 +4689,7 @@
         <v>125898612</v>
       </c>
       <c r="B41" t="n">
-        <v>105358</v>
+        <v>105362</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>125897532</v>
       </c>
       <c r="B42" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125588127</v>
+        <v>125588919</v>
       </c>
       <c r="B2" t="n">
-        <v>57664</v>
+        <v>97220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617343</v>
+        <v>617195</v>
       </c>
       <c r="R2" t="n">
-        <v>6562872</v>
+        <v>6562875</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +743,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>07:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,27 +772,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125587385</v>
+        <v>125588127</v>
       </c>
       <c r="B3" t="n">
-        <v>5196</v>
+        <v>57664</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,22 +800,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617059</v>
+        <v>617343</v>
       </c>
       <c r="R3" t="n">
-        <v>6562493</v>
+        <v>6562872</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,9 +849,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125588919</v>
+        <v>125587385</v>
       </c>
       <c r="B4" t="n">
-        <v>97219</v>
+        <v>5196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,34 +899,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617195</v>
+        <v>617059</v>
       </c>
       <c r="R4" t="n">
-        <v>6562875</v>
+        <v>6562493</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
         <v>125589789</v>
       </c>
       <c r="B5" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>125588011</v>
       </c>
       <c r="B11" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>125587620</v>
       </c>
       <c r="B13" t="n">
-        <v>95787</v>
+        <v>95788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,48 +2003,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125589723</v>
+        <v>125591515</v>
       </c>
       <c r="B15" t="n">
-        <v>96591</v>
+        <v>91861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>617043</v>
+        <v>617222</v>
       </c>
       <c r="R15" t="n">
-        <v>6562446</v>
+        <v>6562777</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2100,48 +2100,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125591515</v>
+        <v>125589723</v>
       </c>
       <c r="B16" t="n">
-        <v>91861</v>
+        <v>96592</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>617222</v>
+        <v>617043</v>
       </c>
       <c r="R16" t="n">
-        <v>6562777</v>
+        <v>6562446</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>125588214</v>
       </c>
       <c r="B17" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>125897482</v>
       </c>
       <c r="B20" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125898363</v>
+        <v>125897879</v>
       </c>
       <c r="B21" t="n">
-        <v>91232</v>
+        <v>96592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,34 +2620,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617347</v>
+        <v>617120</v>
       </c>
       <c r="R21" t="n">
-        <v>6562816</v>
+        <v>6562558</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125898834</v>
+        <v>125898363</v>
       </c>
       <c r="B22" t="n">
-        <v>91252</v>
+        <v>91232</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2717,43 +2717,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617150</v>
+        <v>617347</v>
       </c>
       <c r="R22" t="n">
-        <v>6562910</v>
+        <v>6562816</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2812,10 +2803,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125897879</v>
+        <v>125898834</v>
       </c>
       <c r="B23" t="n">
-        <v>96591</v>
+        <v>91252</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2823,34 +2814,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617120</v>
+        <v>617150</v>
       </c>
       <c r="R23" t="n">
-        <v>6562558</v>
+        <v>6562910</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3011,50 +3011,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125899099</v>
+        <v>125898191</v>
       </c>
       <c r="B25" t="n">
-        <v>8436</v>
+        <v>96592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>616903</v>
+        <v>617135</v>
       </c>
       <c r="R25" t="n">
-        <v>6562497</v>
+        <v>6562631</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3113,45 +3108,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125898191</v>
+        <v>125899099</v>
       </c>
       <c r="B26" t="n">
-        <v>96591</v>
+        <v>8436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>617135</v>
+        <v>616903</v>
       </c>
       <c r="R26" t="n">
-        <v>6562631</v>
+        <v>6562497</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3640,7 +3640,7 @@
         <v>125898500</v>
       </c>
       <c r="B31" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>125897659</v>
       </c>
       <c r="B34" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125897142</v>
+        <v>125898732</v>
       </c>
       <c r="B35" t="n">
-        <v>57809</v>
+        <v>57648</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4046,16 +4046,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4063,31 +4063,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>616889</v>
+        <v>617358</v>
       </c>
       <c r="R35" t="n">
-        <v>6562374</v>
+        <v>6562976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4119,7 +4110,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4129,7 +4120,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4156,50 +4147,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125898732</v>
+        <v>125899125</v>
       </c>
       <c r="B36" t="n">
-        <v>57648</v>
+        <v>8436</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617358</v>
+        <v>616870</v>
       </c>
       <c r="R36" t="n">
-        <v>6562976</v>
+        <v>6562497</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4229,19 +4220,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>08:55</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>08:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4268,50 +4249,59 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125899125</v>
+        <v>125897142</v>
       </c>
       <c r="B37" t="n">
-        <v>8436</v>
+        <v>57809</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106554</v>
+        <v>103020</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616870</v>
+        <v>616889</v>
       </c>
       <c r="R37" t="n">
-        <v>6562497</v>
+        <v>6562374</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4341,9 +4331,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4472,50 +4472,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125898857</v>
+        <v>125898693</v>
       </c>
       <c r="B39" t="n">
-        <v>57648</v>
+        <v>8436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617020</v>
+        <v>617374</v>
       </c>
       <c r="R39" t="n">
-        <v>6562779</v>
+        <v>6562974</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4545,19 +4545,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,50 +4574,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125898693</v>
+        <v>125898857</v>
       </c>
       <c r="B40" t="n">
-        <v>8436</v>
+        <v>57648</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617374</v>
+        <v>617020</v>
       </c>
       <c r="R40" t="n">
-        <v>6562974</v>
+        <v>6562779</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4657,9 +4647,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4689,7 +4689,7 @@
         <v>125898612</v>
       </c>
       <c r="B41" t="n">
-        <v>105362</v>
+        <v>105363</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>125897532</v>
       </c>
       <c r="B42" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125588919</v>
+        <v>125588127</v>
       </c>
       <c r="B2" t="n">
-        <v>97220</v>
+        <v>57664</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617195</v>
+        <v>617343</v>
       </c>
       <c r="R2" t="n">
-        <v>6562875</v>
+        <v>6562872</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +752,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>07:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,27 +791,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125588127</v>
+        <v>125587385</v>
       </c>
       <c r="B3" t="n">
-        <v>57664</v>
+        <v>5196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -800,26 +819,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617343</v>
+        <v>617059</v>
       </c>
       <c r="R3" t="n">
-        <v>6562872</v>
+        <v>6562493</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,19 +864,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>07:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125587385</v>
+        <v>125588919</v>
       </c>
       <c r="B4" t="n">
-        <v>5196</v>
+        <v>97220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,39 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617059</v>
+        <v>617195</v>
       </c>
       <c r="R4" t="n">
-        <v>6562493</v>
+        <v>6562875</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -2003,48 +2003,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125591515</v>
+        <v>125589723</v>
       </c>
       <c r="B15" t="n">
-        <v>91861</v>
+        <v>96592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>617222</v>
+        <v>617043</v>
       </c>
       <c r="R15" t="n">
-        <v>6562777</v>
+        <v>6562446</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2100,48 +2100,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125589723</v>
+        <v>125591515</v>
       </c>
       <c r="B16" t="n">
-        <v>96592</v>
+        <v>91861</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>617043</v>
+        <v>617222</v>
       </c>
       <c r="R16" t="n">
-        <v>6562446</v>
+        <v>6562777</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2294,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125898809</v>
+        <v>125898903</v>
       </c>
       <c r="B18" t="n">
-        <v>91252</v>
+        <v>57648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,46 +2305,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>617125</v>
+        <v>616923</v>
       </c>
       <c r="R18" t="n">
-        <v>6562956</v>
+        <v>6562795</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2371,9 +2367,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2400,10 +2406,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125898903</v>
+        <v>125898809</v>
       </c>
       <c r="B19" t="n">
-        <v>57648</v>
+        <v>91252</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2411,42 +2417,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>bobesök?</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616923</v>
+        <v>617125</v>
       </c>
       <c r="R19" t="n">
-        <v>6562795</v>
+        <v>6562956</v>
       </c>
       <c r="S19" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2473,19 +2483,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3535,10 +3535,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125898677</v>
+        <v>125898500</v>
       </c>
       <c r="B30" t="n">
-        <v>8436</v>
+        <v>98256</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,39 +3546,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617387</v>
+        <v>617391</v>
       </c>
       <c r="R30" t="n">
-        <v>6562949</v>
+        <v>6562882</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3637,10 +3632,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125898500</v>
+        <v>125898677</v>
       </c>
       <c r="B31" t="n">
-        <v>98256</v>
+        <v>8436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3648,34 +3643,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>617391</v>
+        <v>617387</v>
       </c>
       <c r="R31" t="n">
-        <v>6562882</v>
+        <v>6562949</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -2003,48 +2003,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125589723</v>
+        <v>125591515</v>
       </c>
       <c r="B15" t="n">
-        <v>96592</v>
+        <v>91861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>617043</v>
+        <v>617222</v>
       </c>
       <c r="R15" t="n">
-        <v>6562446</v>
+        <v>6562777</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2100,48 +2100,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125591515</v>
+        <v>125589723</v>
       </c>
       <c r="B16" t="n">
-        <v>91861</v>
+        <v>96592</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>617222</v>
+        <v>617043</v>
       </c>
       <c r="R16" t="n">
-        <v>6562777</v>
+        <v>6562446</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2294,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125898903</v>
+        <v>125898809</v>
       </c>
       <c r="B18" t="n">
-        <v>57648</v>
+        <v>91252</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,42 +2305,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bobesök?</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616923</v>
+        <v>617125</v>
       </c>
       <c r="R18" t="n">
-        <v>6562795</v>
+        <v>6562956</v>
       </c>
       <c r="S18" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2367,19 +2371,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,10 +2400,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125898809</v>
+        <v>125898903</v>
       </c>
       <c r="B19" t="n">
-        <v>91252</v>
+        <v>57648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2417,46 +2411,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>617125</v>
+        <v>616923</v>
       </c>
       <c r="R19" t="n">
-        <v>6562956</v>
+        <v>6562795</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2483,9 +2473,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3011,45 +3011,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125898191</v>
+        <v>125899099</v>
       </c>
       <c r="B25" t="n">
-        <v>96592</v>
+        <v>8436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>617135</v>
+        <v>616903</v>
       </c>
       <c r="R25" t="n">
-        <v>6562631</v>
+        <v>6562497</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,50 +3113,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125899099</v>
+        <v>125898191</v>
       </c>
       <c r="B26" t="n">
-        <v>8436</v>
+        <v>96592</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>616903</v>
+        <v>617135</v>
       </c>
       <c r="R26" t="n">
-        <v>6562497</v>
+        <v>6562631</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125898732</v>
+        <v>125897142</v>
       </c>
       <c r="B35" t="n">
-        <v>57648</v>
+        <v>57809</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4046,16 +4046,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4063,22 +4063,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>617358</v>
+        <v>616889</v>
       </c>
       <c r="R35" t="n">
-        <v>6562976</v>
+        <v>6562374</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4110,7 +4119,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4120,7 +4129,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4147,50 +4156,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125899125</v>
+        <v>125898732</v>
       </c>
       <c r="B36" t="n">
-        <v>8436</v>
+        <v>57648</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>616870</v>
+        <v>617358</v>
       </c>
       <c r="R36" t="n">
-        <v>6562497</v>
+        <v>6562976</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4220,9 +4229,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4249,59 +4268,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125897142</v>
+        <v>125899125</v>
       </c>
       <c r="B37" t="n">
-        <v>57809</v>
+        <v>8436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616889</v>
+        <v>616870</v>
       </c>
       <c r="R37" t="n">
-        <v>6562374</v>
+        <v>6562497</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4331,19 +4341,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>07:20</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125588127</v>
       </c>
       <c r="B2" t="n">
-        <v>57664</v>
+        <v>57665</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>125588919</v>
       </c>
       <c r="B4" t="n">
-        <v>97220</v>
+        <v>97222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>125589789</v>
       </c>
       <c r="B5" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>125589867</v>
       </c>
       <c r="B7" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125587652</v>
+        <v>125588805</v>
       </c>
       <c r="B9" t="n">
         <v>8436</v>
@@ -1426,21 +1426,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>617165</v>
+        <v>617207</v>
       </c>
       <c r="R9" t="n">
-        <v>6562682</v>
+        <v>6562981</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1494,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125588805</v>
+        <v>125587652</v>
       </c>
       <c r="B10" t="n">
         <v>8436</v>
@@ -1528,16 +1523,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>617207</v>
+        <v>617165</v>
       </c>
       <c r="R10" t="n">
-        <v>6562981</v>
+        <v>6562682</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,7 +1599,7 @@
         <v>125588011</v>
       </c>
       <c r="B11" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>125587620</v>
       </c>
       <c r="B13" t="n">
-        <v>95788</v>
+        <v>95790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>125591515</v>
       </c>
       <c r="B15" t="n">
-        <v>91861</v>
+        <v>91863</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>125589723</v>
       </c>
       <c r="B16" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>125588214</v>
       </c>
       <c r="B17" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>125898809</v>
       </c>
       <c r="B18" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>125898903</v>
       </c>
       <c r="B19" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>125897482</v>
       </c>
       <c r="B20" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,45 +2609,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125897879</v>
+        <v>125897268</v>
       </c>
       <c r="B21" t="n">
-        <v>96592</v>
+        <v>8436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617120</v>
+        <v>617001</v>
       </c>
       <c r="R21" t="n">
-        <v>6562558</v>
+        <v>6562375</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,10 +2711,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125898363</v>
+        <v>125897879</v>
       </c>
       <c r="B22" t="n">
-        <v>91232</v>
+        <v>96594</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2717,34 +2722,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617347</v>
+        <v>617120</v>
       </c>
       <c r="R22" t="n">
-        <v>6562816</v>
+        <v>6562558</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2803,10 +2808,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125898834</v>
+        <v>125898363</v>
       </c>
       <c r="B23" t="n">
-        <v>91252</v>
+        <v>91234</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2814,43 +2819,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617150</v>
+        <v>617347</v>
       </c>
       <c r="R23" t="n">
-        <v>6562910</v>
+        <v>6562816</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2909,50 +2905,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125897268</v>
+        <v>125898834</v>
       </c>
       <c r="B24" t="n">
-        <v>8436</v>
+        <v>91254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617001</v>
+        <v>617150</v>
       </c>
       <c r="R24" t="n">
-        <v>6562375</v>
+        <v>6562910</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3116,7 +3116,7 @@
         <v>125898191</v>
       </c>
       <c r="B26" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>125898277</v>
       </c>
       <c r="B27" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>125898383</v>
       </c>
       <c r="B28" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3429,54 +3429,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125897235</v>
+        <v>125898500</v>
       </c>
       <c r="B29" t="n">
-        <v>91252</v>
+        <v>98258</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>616952</v>
+        <v>617391</v>
       </c>
       <c r="R29" t="n">
-        <v>6562293</v>
+        <v>6562882</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3535,45 +3526,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125898500</v>
+        <v>125897235</v>
       </c>
       <c r="B30" t="n">
-        <v>98256</v>
+        <v>91254</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617391</v>
+        <v>616952</v>
       </c>
       <c r="R30" t="n">
-        <v>6562882</v>
+        <v>6562293</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3941,7 +3941,7 @@
         <v>125897659</v>
       </c>
       <c r="B34" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125897142</v>
+        <v>125898732</v>
       </c>
       <c r="B35" t="n">
-        <v>57809</v>
+        <v>57649</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4046,16 +4046,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4063,31 +4063,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>616889</v>
+        <v>617358</v>
       </c>
       <c r="R35" t="n">
-        <v>6562374</v>
+        <v>6562976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4119,7 +4110,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4129,7 +4120,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4156,10 +4147,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125898732</v>
+        <v>125897142</v>
       </c>
       <c r="B36" t="n">
-        <v>57648</v>
+        <v>57810</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4167,16 +4158,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4184,22 +4175,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617358</v>
+        <v>616889</v>
       </c>
       <c r="R36" t="n">
-        <v>6562976</v>
+        <v>6562374</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4472,50 +4472,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125898693</v>
+        <v>125898857</v>
       </c>
       <c r="B39" t="n">
-        <v>8436</v>
+        <v>57649</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617374</v>
+        <v>617020</v>
       </c>
       <c r="R39" t="n">
-        <v>6562974</v>
+        <v>6562779</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4545,9 +4545,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4574,50 +4584,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125898857</v>
+        <v>125898693</v>
       </c>
       <c r="B40" t="n">
-        <v>57648</v>
+        <v>8436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617020</v>
+        <v>617374</v>
       </c>
       <c r="R40" t="n">
-        <v>6562779</v>
+        <v>6562974</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4647,19 +4657,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4689,7 +4689,7 @@
         <v>125898612</v>
       </c>
       <c r="B41" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>125897532</v>
       </c>
       <c r="B42" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -2003,48 +2003,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125591515</v>
+        <v>125589723</v>
       </c>
       <c r="B15" t="n">
-        <v>91863</v>
+        <v>96594</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>617222</v>
+        <v>617043</v>
       </c>
       <c r="R15" t="n">
-        <v>6562777</v>
+        <v>6562446</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2100,48 +2100,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125589723</v>
+        <v>125591515</v>
       </c>
       <c r="B16" t="n">
-        <v>96594</v>
+        <v>91863</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>617043</v>
+        <v>617222</v>
       </c>
       <c r="R16" t="n">
-        <v>6562446</v>
+        <v>6562777</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3429,45 +3429,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125898500</v>
+        <v>125897235</v>
       </c>
       <c r="B29" t="n">
-        <v>98258</v>
+        <v>91254</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>617391</v>
+        <v>616952</v>
       </c>
       <c r="R29" t="n">
-        <v>6562882</v>
+        <v>6562293</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3526,54 +3535,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125897235</v>
+        <v>125898500</v>
       </c>
       <c r="B30" t="n">
-        <v>91254</v>
+        <v>98258</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>616952</v>
+        <v>617391</v>
       </c>
       <c r="R30" t="n">
-        <v>6562293</v>
+        <v>6562882</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125587385</v>
+        <v>125588919</v>
       </c>
       <c r="B3" t="n">
-        <v>5196</v>
+        <v>97224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,39 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617059</v>
+        <v>617195</v>
       </c>
       <c r="R3" t="n">
-        <v>6562493</v>
+        <v>6562875</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125588919</v>
+        <v>125587385</v>
       </c>
       <c r="B4" t="n">
-        <v>97222</v>
+        <v>5196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,34 +899,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617195</v>
+        <v>617059</v>
       </c>
       <c r="R4" t="n">
-        <v>6562875</v>
+        <v>6562493</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
         <v>125589789</v>
       </c>
       <c r="B5" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>125589867</v>
       </c>
       <c r="B7" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125588805</v>
+        <v>125587652</v>
       </c>
       <c r="B9" t="n">
         <v>8436</v>
@@ -1426,16 +1426,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>617207</v>
+        <v>617165</v>
       </c>
       <c r="R9" t="n">
-        <v>6562981</v>
+        <v>6562682</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1499,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125587652</v>
+        <v>125588805</v>
       </c>
       <c r="B10" t="n">
         <v>8436</v>
@@ -1523,21 +1528,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>617165</v>
+        <v>617207</v>
       </c>
       <c r="R10" t="n">
-        <v>6562682</v>
+        <v>6562981</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,7 +1599,7 @@
         <v>125588011</v>
       </c>
       <c r="B11" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>125587620</v>
       </c>
       <c r="B13" t="n">
-        <v>95790</v>
+        <v>95792</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>125589723</v>
       </c>
       <c r="B15" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>125591515</v>
       </c>
       <c r="B16" t="n">
-        <v>91863</v>
+        <v>91865</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>125588214</v>
       </c>
       <c r="B17" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125898809</v>
+        <v>125898903</v>
       </c>
       <c r="B18" t="n">
-        <v>91254</v>
+        <v>57649</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,46 +2305,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>617125</v>
+        <v>616923</v>
       </c>
       <c r="R18" t="n">
-        <v>6562956</v>
+        <v>6562795</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2371,9 +2367,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2400,10 +2406,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125898903</v>
+        <v>125898809</v>
       </c>
       <c r="B19" t="n">
-        <v>57649</v>
+        <v>91256</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2411,42 +2417,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>bobesök?</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616923</v>
+        <v>617125</v>
       </c>
       <c r="R19" t="n">
-        <v>6562795</v>
+        <v>6562956</v>
       </c>
       <c r="S19" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2473,19 +2483,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2515,7 +2515,7 @@
         <v>125897482</v>
       </c>
       <c r="B20" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,50 +2609,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125897268</v>
+        <v>125897879</v>
       </c>
       <c r="B21" t="n">
-        <v>8436</v>
+        <v>96596</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617001</v>
+        <v>617120</v>
       </c>
       <c r="R21" t="n">
-        <v>6562375</v>
+        <v>6562558</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,10 +2706,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125897879</v>
+        <v>125898363</v>
       </c>
       <c r="B22" t="n">
-        <v>96594</v>
+        <v>91236</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,34 +2717,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617120</v>
+        <v>617347</v>
       </c>
       <c r="R22" t="n">
-        <v>6562558</v>
+        <v>6562816</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2808,45 +2803,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125898363</v>
+        <v>125897268</v>
       </c>
       <c r="B23" t="n">
-        <v>91234</v>
+        <v>8436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617347</v>
+        <v>617001</v>
       </c>
       <c r="R23" t="n">
-        <v>6562816</v>
+        <v>6562375</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2908,7 +2908,7 @@
         <v>125898834</v>
       </c>
       <c r="B24" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>125898191</v>
       </c>
       <c r="B26" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>125897235</v>
       </c>
       <c r="B29" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125898500</v>
+        <v>125898677</v>
       </c>
       <c r="B30" t="n">
-        <v>98258</v>
+        <v>8436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,34 +3546,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617391</v>
+        <v>617387</v>
       </c>
       <c r="R30" t="n">
-        <v>6562882</v>
+        <v>6562949</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,10 +3637,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125898677</v>
+        <v>125898500</v>
       </c>
       <c r="B31" t="n">
-        <v>8436</v>
+        <v>98260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,39 +3648,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106554</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>617387</v>
+        <v>617391</v>
       </c>
       <c r="R31" t="n">
-        <v>6562949</v>
+        <v>6562882</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3941,7 +3941,7 @@
         <v>125897659</v>
       </c>
       <c r="B34" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>125898612</v>
       </c>
       <c r="B41" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>125897532</v>
       </c>
       <c r="B42" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125588919</v>
+        <v>125587385</v>
       </c>
       <c r="B3" t="n">
-        <v>97224</v>
+        <v>5196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +802,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617195</v>
+        <v>617059</v>
       </c>
       <c r="R3" t="n">
-        <v>6562875</v>
+        <v>6562493</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125587385</v>
+        <v>125588919</v>
       </c>
       <c r="B4" t="n">
-        <v>5196</v>
+        <v>97224</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,39 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617059</v>
+        <v>617195</v>
       </c>
       <c r="R4" t="n">
-        <v>6562493</v>
+        <v>6562875</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -3011,50 +3011,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125899099</v>
+        <v>125898191</v>
       </c>
       <c r="B25" t="n">
-        <v>8436</v>
+        <v>96596</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>616903</v>
+        <v>617135</v>
       </c>
       <c r="R25" t="n">
-        <v>6562497</v>
+        <v>6562631</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3113,45 +3108,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125898191</v>
+        <v>125899099</v>
       </c>
       <c r="B26" t="n">
-        <v>96596</v>
+        <v>8436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>617135</v>
+        <v>616903</v>
       </c>
       <c r="R26" t="n">
-        <v>6562631</v>
+        <v>6562497</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4883,6 +4883,228 @@
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126267992</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98262</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Svartkärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>617397</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6562856</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126264283</v>
+      </c>
+      <c r="B44" t="n">
+        <v>105371</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Svartkärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>617410</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6562726</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125588919</v>
       </c>
       <c r="B4" t="n">
-        <v>97224</v>
+        <v>97226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>125589789</v>
       </c>
       <c r="B5" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>125589867</v>
       </c>
       <c r="B7" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>125588011</v>
       </c>
       <c r="B11" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>125587620</v>
       </c>
       <c r="B13" t="n">
-        <v>95792</v>
+        <v>95794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,48 +2003,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125589723</v>
+        <v>125591515</v>
       </c>
       <c r="B15" t="n">
-        <v>96596</v>
+        <v>91867</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>617043</v>
+        <v>617222</v>
       </c>
       <c r="R15" t="n">
-        <v>6562446</v>
+        <v>6562777</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2100,48 +2100,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125591515</v>
+        <v>125589723</v>
       </c>
       <c r="B16" t="n">
-        <v>91865</v>
+        <v>96598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>617222</v>
+        <v>617043</v>
       </c>
       <c r="R16" t="n">
-        <v>6562777</v>
+        <v>6562446</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>125588214</v>
       </c>
       <c r="B17" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>125898809</v>
       </c>
       <c r="B19" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>125897482</v>
       </c>
       <c r="B20" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125897879</v>
+        <v>125898363</v>
       </c>
       <c r="B21" t="n">
-        <v>96596</v>
+        <v>91238</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,34 +2620,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617120</v>
+        <v>617347</v>
       </c>
       <c r="R21" t="n">
-        <v>6562558</v>
+        <v>6562816</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125898363</v>
+        <v>125897879</v>
       </c>
       <c r="B22" t="n">
-        <v>91236</v>
+        <v>96598</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2717,34 +2717,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617347</v>
+        <v>617120</v>
       </c>
       <c r="R22" t="n">
-        <v>6562816</v>
+        <v>6562558</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2803,50 +2803,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125897268</v>
+        <v>125898834</v>
       </c>
       <c r="B23" t="n">
-        <v>8436</v>
+        <v>91258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617001</v>
+        <v>617150</v>
       </c>
       <c r="R23" t="n">
-        <v>6562375</v>
+        <v>6562910</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2905,54 +2909,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125898834</v>
+        <v>125897268</v>
       </c>
       <c r="B24" t="n">
-        <v>91256</v>
+        <v>8436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617150</v>
+        <v>617001</v>
       </c>
       <c r="R24" t="n">
-        <v>6562910</v>
+        <v>6562375</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
         <v>125898191</v>
       </c>
       <c r="B25" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>125897235</v>
       </c>
       <c r="B29" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>125898500</v>
       </c>
       <c r="B31" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>125897659</v>
       </c>
       <c r="B34" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4472,50 +4472,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125898857</v>
+        <v>125898693</v>
       </c>
       <c r="B39" t="n">
-        <v>57649</v>
+        <v>8436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617020</v>
+        <v>617374</v>
       </c>
       <c r="R39" t="n">
-        <v>6562779</v>
+        <v>6562974</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4545,19 +4545,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,50 +4574,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125898693</v>
+        <v>125898857</v>
       </c>
       <c r="B40" t="n">
-        <v>8436</v>
+        <v>57649</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617374</v>
+        <v>617020</v>
       </c>
       <c r="R40" t="n">
-        <v>6562974</v>
+        <v>6562779</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4657,9 +4647,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4689,7 +4689,7 @@
         <v>125898612</v>
       </c>
       <c r="B41" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>125897532</v>
       </c>
       <c r="B42" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125588127</v>
+        <v>125587385</v>
       </c>
       <c r="B2" t="n">
-        <v>57665</v>
+        <v>5196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,26 +703,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617343</v>
+        <v>617059</v>
       </c>
       <c r="R2" t="n">
-        <v>6562872</v>
+        <v>6562493</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +748,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>07:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,27 +777,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125587385</v>
+        <v>125588127</v>
       </c>
       <c r="B3" t="n">
-        <v>5196</v>
+        <v>57665</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,22 +805,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617059</v>
+        <v>617343</v>
       </c>
       <c r="R3" t="n">
-        <v>6562493</v>
+        <v>6562872</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,9 +854,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2609,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125898363</v>
+        <v>125898834</v>
       </c>
       <c r="B21" t="n">
-        <v>91238</v>
+        <v>91258</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,34 +2620,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617347</v>
+        <v>617150</v>
       </c>
       <c r="R21" t="n">
-        <v>6562816</v>
+        <v>6562910</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,45 +2715,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125897879</v>
+        <v>125897268</v>
       </c>
       <c r="B22" t="n">
-        <v>96598</v>
+        <v>8436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617120</v>
+        <v>617001</v>
       </c>
       <c r="R22" t="n">
-        <v>6562558</v>
+        <v>6562375</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2803,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125898834</v>
+        <v>125898363</v>
       </c>
       <c r="B23" t="n">
-        <v>91258</v>
+        <v>91238</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2814,43 +2828,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617150</v>
+        <v>617347</v>
       </c>
       <c r="R23" t="n">
-        <v>6562910</v>
+        <v>6562816</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2909,50 +2914,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125897268</v>
+        <v>125897879</v>
       </c>
       <c r="B24" t="n">
-        <v>8436</v>
+        <v>96598</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617001</v>
+        <v>617120</v>
       </c>
       <c r="R24" t="n">
-        <v>6562375</v>
+        <v>6562558</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -2297,7 +2297,7 @@
         <v>125898903</v>
       </c>
       <c r="B18" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>125898809</v>
       </c>
       <c r="B19" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>125897482</v>
       </c>
       <c r="B20" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,54 +2609,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125898834</v>
+        <v>125897268</v>
       </c>
       <c r="B21" t="n">
-        <v>91258</v>
+        <v>8436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617150</v>
+        <v>617001</v>
       </c>
       <c r="R21" t="n">
-        <v>6562910</v>
+        <v>6562375</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,50 +2711,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125897268</v>
+        <v>125897879</v>
       </c>
       <c r="B22" t="n">
-        <v>8436</v>
+        <v>96602</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617001</v>
+        <v>617120</v>
       </c>
       <c r="R22" t="n">
-        <v>6562375</v>
+        <v>6562558</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2820,7 +2811,7 @@
         <v>125898363</v>
       </c>
       <c r="B23" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,10 +2905,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125897879</v>
+        <v>125898834</v>
       </c>
       <c r="B24" t="n">
-        <v>96598</v>
+        <v>91262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2925,34 +2916,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617120</v>
+        <v>617150</v>
       </c>
       <c r="R24" t="n">
-        <v>6562558</v>
+        <v>6562910</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
         <v>125898191</v>
       </c>
       <c r="B25" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>125898277</v>
       </c>
       <c r="B27" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>125898383</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>125897235</v>
       </c>
       <c r="B29" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125898677</v>
+        <v>125898500</v>
       </c>
       <c r="B30" t="n">
-        <v>8436</v>
+        <v>98266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,39 +3546,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617387</v>
+        <v>617391</v>
       </c>
       <c r="R30" t="n">
-        <v>6562949</v>
+        <v>6562882</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3637,10 +3632,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125898500</v>
+        <v>125898677</v>
       </c>
       <c r="B31" t="n">
-        <v>98262</v>
+        <v>8436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3648,34 +3643,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>617391</v>
+        <v>617387</v>
       </c>
       <c r="R31" t="n">
-        <v>6562882</v>
+        <v>6562949</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3941,7 +3941,7 @@
         <v>125897659</v>
       </c>
       <c r="B34" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>125898732</v>
       </c>
       <c r="B35" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4147,59 +4147,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125897142</v>
+        <v>125899125</v>
       </c>
       <c r="B36" t="n">
-        <v>57810</v>
+        <v>8436</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>616889</v>
+        <v>616870</v>
       </c>
       <c r="R36" t="n">
-        <v>6562374</v>
+        <v>6562497</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4229,19 +4220,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>07:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4268,50 +4249,59 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125899125</v>
+        <v>125897142</v>
       </c>
       <c r="B37" t="n">
-        <v>8436</v>
+        <v>57814</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106554</v>
+        <v>103020</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616870</v>
+        <v>616889</v>
       </c>
       <c r="R37" t="n">
-        <v>6562497</v>
+        <v>6562374</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4341,9 +4331,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4472,50 +4472,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125898693</v>
+        <v>125898857</v>
       </c>
       <c r="B39" t="n">
-        <v>8436</v>
+        <v>57653</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617374</v>
+        <v>617020</v>
       </c>
       <c r="R39" t="n">
-        <v>6562974</v>
+        <v>6562779</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4545,9 +4545,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4574,50 +4584,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125898857</v>
+        <v>125898693</v>
       </c>
       <c r="B40" t="n">
-        <v>57649</v>
+        <v>8436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617020</v>
+        <v>617374</v>
       </c>
       <c r="R40" t="n">
-        <v>6562779</v>
+        <v>6562974</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4647,19 +4657,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4689,7 +4689,7 @@
         <v>125898612</v>
       </c>
       <c r="B41" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>125897532</v>
       </c>
       <c r="B42" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>126267992</v>
       </c>
       <c r="B43" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>126264283</v>
       </c>
       <c r="B44" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -2294,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125898903</v>
+        <v>125898809</v>
       </c>
       <c r="B18" t="n">
-        <v>57653</v>
+        <v>91262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,42 +2305,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bobesök?</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616923</v>
+        <v>617125</v>
       </c>
       <c r="R18" t="n">
-        <v>6562795</v>
+        <v>6562956</v>
       </c>
       <c r="S18" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2367,19 +2371,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,10 +2400,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125898809</v>
+        <v>125898903</v>
       </c>
       <c r="B19" t="n">
-        <v>91262</v>
+        <v>57653</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2417,46 +2411,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>617125</v>
+        <v>616923</v>
       </c>
       <c r="R19" t="n">
-        <v>6562956</v>
+        <v>6562795</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2483,9 +2473,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3429,54 +3429,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125897235</v>
+        <v>125898677</v>
       </c>
       <c r="B29" t="n">
-        <v>91262</v>
+        <v>8436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>616952</v>
+        <v>617387</v>
       </c>
       <c r="R29" t="n">
-        <v>6562293</v>
+        <v>6562949</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3535,45 +3531,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125898500</v>
+        <v>125897235</v>
       </c>
       <c r="B30" t="n">
-        <v>98266</v>
+        <v>91262</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617391</v>
+        <v>616952</v>
       </c>
       <c r="R30" t="n">
-        <v>6562882</v>
+        <v>6562293</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,10 +3637,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125898677</v>
+        <v>125898500</v>
       </c>
       <c r="B31" t="n">
-        <v>8436</v>
+        <v>98266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,39 +3648,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106554</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>617387</v>
+        <v>617391</v>
       </c>
       <c r="R31" t="n">
-        <v>6562949</v>
+        <v>6562882</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4147,50 +4147,59 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125899125</v>
+        <v>125897142</v>
       </c>
       <c r="B36" t="n">
-        <v>8436</v>
+        <v>57814</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>103020</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>616870</v>
+        <v>616889</v>
       </c>
       <c r="R36" t="n">
-        <v>6562497</v>
+        <v>6562374</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4220,9 +4229,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4249,59 +4268,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125897142</v>
+        <v>125899125</v>
       </c>
       <c r="B37" t="n">
-        <v>57814</v>
+        <v>8436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616889</v>
+        <v>616870</v>
       </c>
       <c r="R37" t="n">
-        <v>6562374</v>
+        <v>6562497</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4331,19 +4341,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>07:20</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2294,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125898809</v>
+        <v>125898903</v>
       </c>
       <c r="B18" t="n">
-        <v>91262</v>
+        <v>57653</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,46 +2305,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>617125</v>
+        <v>616923</v>
       </c>
       <c r="R18" t="n">
-        <v>6562956</v>
+        <v>6562795</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2371,9 +2367,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2400,10 +2406,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125898903</v>
+        <v>125898809</v>
       </c>
       <c r="B19" t="n">
-        <v>57653</v>
+        <v>91262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2411,42 +2417,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>bobesök?</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616923</v>
+        <v>617125</v>
       </c>
       <c r="R19" t="n">
-        <v>6562795</v>
+        <v>6562956</v>
       </c>
       <c r="S19" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2473,19 +2483,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2515,7 +2515,7 @@
         <v>125897482</v>
       </c>
       <c r="B20" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,50 +2609,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125897268</v>
+        <v>125898834</v>
       </c>
       <c r="B21" t="n">
-        <v>8436</v>
+        <v>91262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617001</v>
+        <v>617150</v>
       </c>
       <c r="R21" t="n">
-        <v>6562375</v>
+        <v>6562910</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2714,7 +2718,7 @@
         <v>125897879</v>
       </c>
       <c r="B22" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2905,54 +2909,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125898834</v>
+        <v>125897268</v>
       </c>
       <c r="B24" t="n">
-        <v>91262</v>
+        <v>8436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617150</v>
+        <v>617001</v>
       </c>
       <c r="R24" t="n">
-        <v>6562910</v>
+        <v>6562375</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
         <v>125898191</v>
       </c>
       <c r="B25" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3429,50 +3429,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125898677</v>
+        <v>125897235</v>
       </c>
       <c r="B29" t="n">
-        <v>8436</v>
+        <v>91262</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>617387</v>
+        <v>616952</v>
       </c>
       <c r="R29" t="n">
-        <v>6562949</v>
+        <v>6562293</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,54 +3535,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125897235</v>
+        <v>125898677</v>
       </c>
       <c r="B30" t="n">
-        <v>91262</v>
+        <v>8436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>616952</v>
+        <v>617387</v>
       </c>
       <c r="R30" t="n">
-        <v>6562293</v>
+        <v>6562949</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3640,7 +3640,7 @@
         <v>125898500</v>
       </c>
       <c r="B31" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>125897659</v>
       </c>
       <c r="B34" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125898732</v>
+        <v>125897142</v>
       </c>
       <c r="B35" t="n">
-        <v>57653</v>
+        <v>57814</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4046,16 +4046,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4063,22 +4063,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>617358</v>
+        <v>616889</v>
       </c>
       <c r="R35" t="n">
-        <v>6562976</v>
+        <v>6562374</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4110,7 +4119,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4120,7 +4129,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4147,59 +4156,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125897142</v>
+        <v>125899125</v>
       </c>
       <c r="B36" t="n">
-        <v>57814</v>
+        <v>8436</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>616889</v>
+        <v>616870</v>
       </c>
       <c r="R36" t="n">
-        <v>6562374</v>
+        <v>6562497</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4229,19 +4229,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>07:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4268,50 +4258,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125899125</v>
+        <v>125898732</v>
       </c>
       <c r="B37" t="n">
-        <v>8436</v>
+        <v>57653</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616870</v>
+        <v>617358</v>
       </c>
       <c r="R37" t="n">
-        <v>6562497</v>
+        <v>6562976</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4341,9 +4331,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4472,50 +4472,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125898857</v>
+        <v>125898693</v>
       </c>
       <c r="B39" t="n">
-        <v>57653</v>
+        <v>8436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617020</v>
+        <v>617374</v>
       </c>
       <c r="R39" t="n">
-        <v>6562779</v>
+        <v>6562974</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4545,19 +4545,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,50 +4574,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125898693</v>
+        <v>125898857</v>
       </c>
       <c r="B40" t="n">
-        <v>8436</v>
+        <v>57653</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617374</v>
+        <v>617020</v>
       </c>
       <c r="R40" t="n">
-        <v>6562974</v>
+        <v>6562779</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4657,9 +4647,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4689,7 +4689,7 @@
         <v>125898612</v>
       </c>
       <c r="B41" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>125897532</v>
       </c>
       <c r="B42" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>126267992</v>
       </c>
       <c r="B43" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>126264283</v>
       </c>
       <c r="B44" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5104,6 +5104,553 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126384255</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91242</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Penningdroget, Penningdroget, Srm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>617291</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6562925</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126392521</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98269</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>617210</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6562715</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126392663</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98389</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>617185</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6562722</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126384487</v>
+      </c>
+      <c r="B48" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Penningdroget, Penningdroget, Srm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>617295</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6562910</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126393198</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98269</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>617328</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6562984</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>19:43</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>19:43</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2609,54 +2609,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125898834</v>
+        <v>125897268</v>
       </c>
       <c r="B21" t="n">
-        <v>91262</v>
+        <v>8436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617150</v>
+        <v>617001</v>
       </c>
       <c r="R21" t="n">
-        <v>6562910</v>
+        <v>6562375</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2711,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125897879</v>
+        <v>125898834</v>
       </c>
       <c r="B22" t="n">
-        <v>96605</v>
+        <v>91262</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2726,34 +2722,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617120</v>
+        <v>617150</v>
       </c>
       <c r="R22" t="n">
-        <v>6562558</v>
+        <v>6562910</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2812,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125898363</v>
+        <v>125897879</v>
       </c>
       <c r="B23" t="n">
-        <v>91242</v>
+        <v>96605</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2823,34 +2828,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617347</v>
+        <v>617120</v>
       </c>
       <c r="R23" t="n">
-        <v>6562816</v>
+        <v>6562558</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2909,50 +2914,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125897268</v>
+        <v>125898363</v>
       </c>
       <c r="B24" t="n">
-        <v>8436</v>
+        <v>91242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617001</v>
+        <v>617347</v>
       </c>
       <c r="R24" t="n">
-        <v>6562375</v>
+        <v>6562816</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4472,50 +4472,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125898693</v>
+        <v>125898857</v>
       </c>
       <c r="B39" t="n">
-        <v>8436</v>
+        <v>57653</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617374</v>
+        <v>617020</v>
       </c>
       <c r="R39" t="n">
-        <v>6562974</v>
+        <v>6562779</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4545,9 +4545,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4574,50 +4584,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125898857</v>
+        <v>125898693</v>
       </c>
       <c r="B40" t="n">
-        <v>57653</v>
+        <v>8436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617020</v>
+        <v>617374</v>
       </c>
       <c r="R40" t="n">
-        <v>6562779</v>
+        <v>6562974</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4647,19 +4657,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5652,6 +5652,332 @@
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126398427</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91242</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>617300</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6562921</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På samma granlåga som rosenticka och granticka.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126398444</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91260</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>617300</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6562921</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På samma granlåga som rosenticka.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126398418</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91538</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>658</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>617300</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6562921</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>8 fruktkroppar nära roten på fälld torrgran.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2294,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125898903</v>
+        <v>125898809</v>
       </c>
       <c r="B18" t="n">
-        <v>57653</v>
+        <v>91262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,42 +2305,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bobesök?</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616923</v>
+        <v>617125</v>
       </c>
       <c r="R18" t="n">
-        <v>6562795</v>
+        <v>6562956</v>
       </c>
       <c r="S18" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2367,19 +2371,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,10 +2400,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125898809</v>
+        <v>125898903</v>
       </c>
       <c r="B19" t="n">
-        <v>91262</v>
+        <v>57653</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2417,46 +2411,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>617125</v>
+        <v>616923</v>
       </c>
       <c r="R19" t="n">
-        <v>6562956</v>
+        <v>6562795</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2483,9 +2473,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,50 +2609,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125897268</v>
+        <v>125897879</v>
       </c>
       <c r="B21" t="n">
-        <v>8436</v>
+        <v>96605</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617001</v>
+        <v>617120</v>
       </c>
       <c r="R21" t="n">
-        <v>6562375</v>
+        <v>6562558</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,54 +2706,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125898834</v>
+        <v>125897268</v>
       </c>
       <c r="B22" t="n">
-        <v>91262</v>
+        <v>8436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617150</v>
+        <v>617001</v>
       </c>
       <c r="R22" t="n">
-        <v>6562910</v>
+        <v>6562375</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2808,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125897879</v>
+        <v>125898363</v>
       </c>
       <c r="B23" t="n">
-        <v>96605</v>
+        <v>91242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,34 +2819,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617120</v>
+        <v>617347</v>
       </c>
       <c r="R23" t="n">
-        <v>6562558</v>
+        <v>6562816</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2914,10 +2905,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125898363</v>
+        <v>125898834</v>
       </c>
       <c r="B24" t="n">
-        <v>91242</v>
+        <v>91262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2925,34 +2916,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617347</v>
+        <v>617150</v>
       </c>
       <c r="R24" t="n">
-        <v>6562816</v>
+        <v>6562910</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125897142</v>
+        <v>125898732</v>
       </c>
       <c r="B35" t="n">
-        <v>57814</v>
+        <v>57653</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4046,16 +4046,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4063,31 +4063,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>616889</v>
+        <v>617358</v>
       </c>
       <c r="R35" t="n">
-        <v>6562374</v>
+        <v>6562976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4119,7 +4110,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4129,7 +4120,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4258,10 +4249,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125898732</v>
+        <v>125897142</v>
       </c>
       <c r="B37" t="n">
-        <v>57653</v>
+        <v>57814</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4269,16 +4260,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4286,22 +4277,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>617358</v>
+        <v>616889</v>
       </c>
       <c r="R37" t="n">
-        <v>6562976</v>
+        <v>6562374</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5978,6 +5978,1934 @@
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126444060</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91260</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>617130</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6562704</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På grenar av torrgran. Riklig förekomst av död ved i form av torrträd och lågor av barkborreangripna granar. Området är svårframkomligt på grund av mängden lågor. Beståndet betingar höga naturvärden knutna till mängden död ved, förekomsten av gamla träd av främst tall med inslag av gran och asp.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126444187</v>
+      </c>
+      <c r="B54" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>617115</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6562825</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Gnagspår på granlåga..</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126444149</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92532</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>617081</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6562799</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Fjolårsex.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126444240</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91207</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>617156</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6562842</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126444262</v>
+      </c>
+      <c r="B57" t="n">
+        <v>97234</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>617220</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6562873</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126443823</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91260</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>617182</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6562740</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På grenar av gammal levande gran.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126443673</v>
+      </c>
+      <c r="B59" t="n">
+        <v>96605</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>53</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>617272</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6562775</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På gammal tallåga.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126443783</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91260</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>617221</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6562770</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På grenar av levande gammal gran.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126444123</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91262</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Käringtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>616908</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6562564</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126443196</v>
+      </c>
+      <c r="B62" t="n">
+        <v>43934</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>617351</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6562861</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126443454</v>
+      </c>
+      <c r="B63" t="n">
+        <v>43934</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>617361</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6562948</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126387235</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91242</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Svartkärret, Svartkärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>617388</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6562792</v>
+      </c>
+      <c r="S64" t="n">
+        <v>35</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126442847</v>
+      </c>
+      <c r="B65" t="n">
+        <v>43934</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>617320</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6563005</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Gnagspår i fnöskticka på gammal björklåga. Flera observerade fynd inom området. Gott om lågor och högstubbar av björk.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126443504</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5196</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>617308</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6562957</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Gnagspår på stammen av torrgran.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126384636</v>
+      </c>
+      <c r="B67" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Svartkärret, Svartkärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>617299</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6562881</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126443868</v>
+      </c>
+      <c r="B68" t="n">
+        <v>97234</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>617125</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6562711</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Riklig lokal.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126443623</v>
+      </c>
+      <c r="B69" t="n">
+        <v>96605</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>53</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>617291</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6562787</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På gammal tallåga. Gammal flerskiktad barrsumpskog med inslag av björk och enstaka asp. Inslag av död ved i form av torrträd, högstubbar och gamla lågor av både gran, tall och björk.</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126443737</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57653</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Årby Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>617250</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6562767</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Hackspår vid roten på gammal torrtall.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -2294,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125898809</v>
+        <v>125898903</v>
       </c>
       <c r="B18" t="n">
-        <v>91262</v>
+        <v>57653</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,46 +2305,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>617125</v>
+        <v>616923</v>
       </c>
       <c r="R18" t="n">
-        <v>6562956</v>
+        <v>6562795</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2371,9 +2367,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2400,10 +2406,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125898903</v>
+        <v>125898809</v>
       </c>
       <c r="B19" t="n">
-        <v>57653</v>
+        <v>91262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2411,42 +2417,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>bobesök?</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616923</v>
+        <v>617125</v>
       </c>
       <c r="R19" t="n">
-        <v>6562795</v>
+        <v>6562956</v>
       </c>
       <c r="S19" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2473,19 +2483,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,50 +2706,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125897268</v>
+        <v>125898363</v>
       </c>
       <c r="B22" t="n">
-        <v>8436</v>
+        <v>91242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617001</v>
+        <v>617347</v>
       </c>
       <c r="R22" t="n">
-        <v>6562375</v>
+        <v>6562816</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2808,10 +2803,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125898363</v>
+        <v>125898834</v>
       </c>
       <c r="B23" t="n">
-        <v>91242</v>
+        <v>91262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2819,34 +2814,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617347</v>
+        <v>617150</v>
       </c>
       <c r="R23" t="n">
-        <v>6562816</v>
+        <v>6562910</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2905,54 +2909,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125898834</v>
+        <v>125897268</v>
       </c>
       <c r="B24" t="n">
-        <v>91262</v>
+        <v>8436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617150</v>
+        <v>617001</v>
       </c>
       <c r="R24" t="n">
-        <v>6562910</v>
+        <v>6562375</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3011,45 +3011,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125898191</v>
+        <v>125899099</v>
       </c>
       <c r="B25" t="n">
-        <v>96605</v>
+        <v>8436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>617135</v>
+        <v>616903</v>
       </c>
       <c r="R25" t="n">
-        <v>6562631</v>
+        <v>6562497</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,50 +3113,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125899099</v>
+        <v>125898191</v>
       </c>
       <c r="B26" t="n">
-        <v>8436</v>
+        <v>96605</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>616903</v>
+        <v>617135</v>
       </c>
       <c r="R26" t="n">
-        <v>6562497</v>
+        <v>6562631</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -2297,7 +2297,7 @@
         <v>125898903</v>
       </c>
       <c r="B18" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>125898809</v>
       </c>
       <c r="B19" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>125897482</v>
       </c>
       <c r="B20" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125897879</v>
+        <v>125898834</v>
       </c>
       <c r="B21" t="n">
-        <v>96605</v>
+        <v>91265</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,34 +2620,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617120</v>
+        <v>617150</v>
       </c>
       <c r="R21" t="n">
-        <v>6562558</v>
+        <v>6562910</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2709,7 +2718,7 @@
         <v>125898363</v>
       </c>
       <c r="B22" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2803,10 +2812,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125898834</v>
+        <v>125897879</v>
       </c>
       <c r="B23" t="n">
-        <v>91262</v>
+        <v>96614</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2814,43 +2823,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617150</v>
+        <v>617120</v>
       </c>
       <c r="R23" t="n">
-        <v>6562910</v>
+        <v>6562558</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3011,50 +3011,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125899099</v>
+        <v>125898191</v>
       </c>
       <c r="B25" t="n">
-        <v>8436</v>
+        <v>96614</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>616903</v>
+        <v>617135</v>
       </c>
       <c r="R25" t="n">
-        <v>6562497</v>
+        <v>6562631</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3113,45 +3108,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125898191</v>
+        <v>125899099</v>
       </c>
       <c r="B26" t="n">
-        <v>96605</v>
+        <v>8436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>617135</v>
+        <v>616903</v>
       </c>
       <c r="R26" t="n">
-        <v>6562631</v>
+        <v>6562497</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3213,7 +3213,7 @@
         <v>125898277</v>
       </c>
       <c r="B27" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>125898383</v>
       </c>
       <c r="B28" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>125897235</v>
       </c>
       <c r="B29" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>125898500</v>
       </c>
       <c r="B31" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>125897659</v>
       </c>
       <c r="B34" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>125898732</v>
       </c>
       <c r="B35" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4147,50 +4147,59 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125899125</v>
+        <v>125897142</v>
       </c>
       <c r="B36" t="n">
-        <v>8436</v>
+        <v>57815</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>103020</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>616870</v>
+        <v>616889</v>
       </c>
       <c r="R36" t="n">
-        <v>6562497</v>
+        <v>6562374</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4220,9 +4229,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4249,59 +4268,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125897142</v>
+        <v>125899125</v>
       </c>
       <c r="B37" t="n">
-        <v>57814</v>
+        <v>8436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616889</v>
+        <v>616870</v>
       </c>
       <c r="R37" t="n">
-        <v>6562374</v>
+        <v>6562497</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4331,19 +4341,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>07:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4475,7 +4475,7 @@
         <v>125898857</v>
       </c>
       <c r="B39" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>125898612</v>
       </c>
       <c r="B41" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>125897532</v>
       </c>
       <c r="B42" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>126267992</v>
       </c>
       <c r="B43" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>126264283</v>
       </c>
       <c r="B44" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>126384255</v>
       </c>
       <c r="B45" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>126392521</v>
       </c>
       <c r="B46" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>126392663</v>
       </c>
       <c r="B47" t="n">
-        <v>98389</v>
+        <v>98398</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>126393198</v>
       </c>
       <c r="B49" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>126398427</v>
       </c>
       <c r="B50" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>126398444</v>
       </c>
       <c r="B51" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>126398418</v>
       </c>
       <c r="B52" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>126444060</v>
       </c>
       <c r="B53" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>126444149</v>
       </c>
       <c r="B55" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>126444240</v>
       </c>
       <c r="B56" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6410,34 +6410,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126444262</v>
+        <v>126443823</v>
       </c>
       <c r="B57" t="n">
-        <v>97234</v>
+        <v>91263</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>224364</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6445,10 +6448,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>617220</v>
+        <v>617182</v>
       </c>
       <c r="R57" t="n">
-        <v>6562873</v>
+        <v>6562740</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6481,6 +6484,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På grenar av gammal levande gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6508,37 +6516,34 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126443823</v>
+        <v>126444262</v>
       </c>
       <c r="B58" t="n">
-        <v>91260</v>
+        <v>97243</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>224364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6546,10 +6551,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>617182</v>
+        <v>617220</v>
       </c>
       <c r="R58" t="n">
-        <v>6562740</v>
+        <v>6562873</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6582,11 +6587,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På grenar av gammal levande gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6617,7 +6617,7 @@
         <v>126443673</v>
       </c>
       <c r="B59" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>126443783</v>
       </c>
       <c r="B60" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>126444123</v>
       </c>
       <c r="B61" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>126443196</v>
       </c>
       <c r="B62" t="n">
-        <v>43934</v>
+        <v>43935</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>126443454</v>
       </c>
       <c r="B63" t="n">
-        <v>43934</v>
+        <v>43935</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>126387235</v>
       </c>
       <c r="B64" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>126442847</v>
       </c>
       <c r="B65" t="n">
-        <v>43934</v>
+        <v>43935</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>126443868</v>
       </c>
       <c r="B68" t="n">
-        <v>97234</v>
+        <v>97243</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>126443623</v>
       </c>
       <c r="B69" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>126443737</v>
       </c>
       <c r="B70" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -2294,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125898903</v>
+        <v>125898809</v>
       </c>
       <c r="B18" t="n">
-        <v>57654</v>
+        <v>91265</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,42 +2305,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bobesök?</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616923</v>
+        <v>617125</v>
       </c>
       <c r="R18" t="n">
-        <v>6562795</v>
+        <v>6562956</v>
       </c>
       <c r="S18" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2367,19 +2371,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,10 +2400,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125898809</v>
+        <v>125898903</v>
       </c>
       <c r="B19" t="n">
-        <v>91265</v>
+        <v>57654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2417,46 +2411,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>617125</v>
+        <v>616923</v>
       </c>
       <c r="R19" t="n">
-        <v>6562956</v>
+        <v>6562795</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2483,9 +2473,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,54 +2609,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125898834</v>
+        <v>125897268</v>
       </c>
       <c r="B21" t="n">
-        <v>91265</v>
+        <v>8436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617150</v>
+        <v>617001</v>
       </c>
       <c r="R21" t="n">
-        <v>6562910</v>
+        <v>6562375</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2711,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125898363</v>
+        <v>125898834</v>
       </c>
       <c r="B22" t="n">
-        <v>91245</v>
+        <v>91265</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2726,34 +2722,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617347</v>
+        <v>617150</v>
       </c>
       <c r="R22" t="n">
-        <v>6562816</v>
+        <v>6562910</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2909,50 +2914,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125897268</v>
+        <v>125898363</v>
       </c>
       <c r="B24" t="n">
-        <v>8436</v>
+        <v>91245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617001</v>
+        <v>617347</v>
       </c>
       <c r="R24" t="n">
-        <v>6562375</v>
+        <v>6562816</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3011,45 +3011,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125898191</v>
+        <v>125899099</v>
       </c>
       <c r="B25" t="n">
-        <v>96614</v>
+        <v>8436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>617135</v>
+        <v>616903</v>
       </c>
       <c r="R25" t="n">
-        <v>6562631</v>
+        <v>6562497</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,50 +3113,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125899099</v>
+        <v>125898191</v>
       </c>
       <c r="B26" t="n">
-        <v>8436</v>
+        <v>96614</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>616903</v>
+        <v>617135</v>
       </c>
       <c r="R26" t="n">
-        <v>6562497</v>
+        <v>6562631</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125898677</v>
+        <v>125898500</v>
       </c>
       <c r="B30" t="n">
-        <v>8436</v>
+        <v>98278</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,39 +3546,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617387</v>
+        <v>617391</v>
       </c>
       <c r="R30" t="n">
-        <v>6562949</v>
+        <v>6562882</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3637,10 +3632,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125898500</v>
+        <v>125898677</v>
       </c>
       <c r="B31" t="n">
-        <v>98278</v>
+        <v>8436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3648,34 +3643,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>617391</v>
+        <v>617387</v>
       </c>
       <c r="R31" t="n">
-        <v>6562882</v>
+        <v>6562949</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125898732</v>
+        <v>125897142</v>
       </c>
       <c r="B35" t="n">
-        <v>57654</v>
+        <v>57815</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4046,16 +4046,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4063,22 +4063,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>617358</v>
+        <v>616889</v>
       </c>
       <c r="R35" t="n">
-        <v>6562976</v>
+        <v>6562374</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4110,7 +4119,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4120,7 +4129,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4147,10 +4156,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125897142</v>
+        <v>125898732</v>
       </c>
       <c r="B36" t="n">
-        <v>57815</v>
+        <v>57654</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4158,16 +4167,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4175,31 +4184,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>616889</v>
+        <v>617358</v>
       </c>
       <c r="R36" t="n">
-        <v>6562374</v>
+        <v>6562976</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -6086,10 +6086,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126444187</v>
+        <v>126444149</v>
       </c>
       <c r="B54" t="n">
-        <v>5176</v>
+        <v>92535</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6097,32 +6097,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6130,10 +6124,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>617115</v>
+        <v>617081</v>
       </c>
       <c r="R54" t="n">
-        <v>6562825</v>
+        <v>6562799</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6170,7 +6164,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Gnagspår på granlåga..</t>
+          <t>Fjolårsex.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6198,10 +6192,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126444149</v>
+        <v>126444187</v>
       </c>
       <c r="B55" t="n">
-        <v>92535</v>
+        <v>5176</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6209,26 +6203,32 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6236,10 +6236,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>617081</v>
+        <v>617115</v>
       </c>
       <c r="R55" t="n">
-        <v>6562799</v>
+        <v>6562825</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Fjolårsex.</t>
+          <t>Gnagspår på granlåga..</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6721,37 +6721,43 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126443783</v>
+        <v>126443196</v>
       </c>
       <c r="B60" t="n">
-        <v>91263</v>
+        <v>43935</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>101735</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6759,10 +6765,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>617221</v>
+        <v>617351</v>
       </c>
       <c r="R60" t="n">
-        <v>6562770</v>
+        <v>6562861</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6795,11 +6801,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På grenar av levande gammal gran.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6827,10 +6828,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126444123</v>
+        <v>126443783</v>
       </c>
       <c r="B61" t="n">
-        <v>91265</v>
+        <v>91263</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6838,45 +6839,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>616908</v>
+        <v>617221</v>
       </c>
       <c r="R61" t="n">
-        <v>6562564</v>
+        <v>6562770</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6909,6 +6902,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På grenar av levande gammal gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6936,54 +6934,56 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126443196</v>
+        <v>126444123</v>
       </c>
       <c r="B62" t="n">
-        <v>43935</v>
+        <v>91265</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>101735</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>617351</v>
+        <v>616908</v>
       </c>
       <c r="R62" t="n">
-        <v>6562861</v>
+        <v>6562564</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7481,10 +7481,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126384636</v>
+        <v>126443868</v>
       </c>
       <c r="B67" t="n">
-        <v>5176</v>
+        <v>97243</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7492,37 +7492,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100526</v>
+        <v>224364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>617299</v>
+        <v>617125</v>
       </c>
       <c r="R67" t="n">
-        <v>6562881</v>
+        <v>6562711</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7549,19 +7549,14 @@
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:52</t>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Riklig lokal.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7570,28 +7565,29 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Johan Björkstén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johan Björkstén</t>
+          <t>Bo Törnquist, Johan Björkstén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126443868</v>
+        <v>126384636</v>
       </c>
       <c r="B68" t="n">
-        <v>97243</v>
+        <v>5176</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7599,37 +7595,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>224364</v>
+        <v>100526</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>617125</v>
+        <v>617299</v>
       </c>
       <c r="R68" t="n">
-        <v>6562711</v>
+        <v>6562881</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7656,14 +7652,19 @@
           <t>2025-07-03</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Riklig lokal.</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7672,19 +7673,18 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Johan Björkstén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén</t>
+          <t>Johan Björkstén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -2294,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125898809</v>
+        <v>125898903</v>
       </c>
       <c r="B18" t="n">
-        <v>91265</v>
+        <v>57654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,46 +2305,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>617125</v>
+        <v>616923</v>
       </c>
       <c r="R18" t="n">
-        <v>6562956</v>
+        <v>6562795</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2371,9 +2367,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2400,10 +2406,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125898903</v>
+        <v>125898809</v>
       </c>
       <c r="B19" t="n">
-        <v>57654</v>
+        <v>91265</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2411,42 +2417,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>bobesök?</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616923</v>
+        <v>617125</v>
       </c>
       <c r="R19" t="n">
-        <v>6562795</v>
+        <v>6562956</v>
       </c>
       <c r="S19" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2473,19 +2483,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,10 +2711,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125898834</v>
+        <v>125898363</v>
       </c>
       <c r="B22" t="n">
-        <v>91265</v>
+        <v>91245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,43 +2722,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617150</v>
+        <v>617347</v>
       </c>
       <c r="R22" t="n">
-        <v>6562910</v>
+        <v>6562816</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2914,10 +2905,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125898363</v>
+        <v>125898834</v>
       </c>
       <c r="B24" t="n">
-        <v>91245</v>
+        <v>91265</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2925,34 +2916,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617347</v>
+        <v>617150</v>
       </c>
       <c r="R24" t="n">
-        <v>6562816</v>
+        <v>6562910</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3011,50 +3011,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125899099</v>
+        <v>125898191</v>
       </c>
       <c r="B25" t="n">
-        <v>8436</v>
+        <v>96614</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>616903</v>
+        <v>617135</v>
       </c>
       <c r="R25" t="n">
-        <v>6562497</v>
+        <v>6562631</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3113,45 +3108,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125898191</v>
+        <v>125899099</v>
       </c>
       <c r="B26" t="n">
-        <v>96614</v>
+        <v>8436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>617135</v>
+        <v>616903</v>
       </c>
       <c r="R26" t="n">
-        <v>6562631</v>
+        <v>6562497</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3429,54 +3429,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125897235</v>
+        <v>125898677</v>
       </c>
       <c r="B29" t="n">
-        <v>91265</v>
+        <v>8436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>616952</v>
+        <v>617387</v>
       </c>
       <c r="R29" t="n">
-        <v>6562293</v>
+        <v>6562949</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3535,45 +3531,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125898500</v>
+        <v>125897235</v>
       </c>
       <c r="B30" t="n">
-        <v>98278</v>
+        <v>91265</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617391</v>
+        <v>616952</v>
       </c>
       <c r="R30" t="n">
-        <v>6562882</v>
+        <v>6562293</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,10 +3637,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125898677</v>
+        <v>125898500</v>
       </c>
       <c r="B31" t="n">
-        <v>8436</v>
+        <v>98278</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,39 +3648,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106554</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>617387</v>
+        <v>617391</v>
       </c>
       <c r="R31" t="n">
-        <v>6562949</v>
+        <v>6562882</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -6721,43 +6721,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126443196</v>
+        <v>126443783</v>
       </c>
       <c r="B60" t="n">
-        <v>43935</v>
+        <v>91263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>101735</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6765,10 +6759,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>617351</v>
+        <v>617221</v>
       </c>
       <c r="R60" t="n">
-        <v>6562861</v>
+        <v>6562770</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6801,6 +6795,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På grenar av levande gammal gran.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6828,10 +6827,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126443783</v>
+        <v>126444123</v>
       </c>
       <c r="B61" t="n">
-        <v>91263</v>
+        <v>91265</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6839,37 +6838,45 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>617221</v>
+        <v>616908</v>
       </c>
       <c r="R61" t="n">
-        <v>6562770</v>
+        <v>6562564</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6902,11 +6909,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På grenar av levande gammal gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6934,56 +6936,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126444123</v>
+        <v>126443196</v>
       </c>
       <c r="B62" t="n">
-        <v>91265</v>
+        <v>43935</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>101735</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>616908</v>
+        <v>617351</v>
       </c>
       <c r="R62" t="n">
-        <v>6562564</v>
+        <v>6562861</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7481,10 +7481,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126443868</v>
+        <v>126384636</v>
       </c>
       <c r="B67" t="n">
-        <v>97243</v>
+        <v>5176</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7492,37 +7492,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>224364</v>
+        <v>100526</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>617125</v>
+        <v>617299</v>
       </c>
       <c r="R67" t="n">
-        <v>6562711</v>
+        <v>6562881</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7549,14 +7549,19 @@
           <t>2025-07-03</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Riklig lokal.</t>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7565,29 +7570,28 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Johan Björkstén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén</t>
+          <t>Johan Björkstén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126384636</v>
+        <v>126443868</v>
       </c>
       <c r="B68" t="n">
-        <v>5176</v>
+        <v>97243</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7595,37 +7599,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100526</v>
+        <v>224364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>617299</v>
+        <v>617125</v>
       </c>
       <c r="R68" t="n">
-        <v>6562881</v>
+        <v>6562711</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7652,19 +7656,14 @@
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>12:52</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Riklig lokal.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7673,18 +7672,19 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johan Björkstén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johan Björkstén</t>
+          <t>Bo Törnquist, Johan Björkstén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -2294,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125898903</v>
+        <v>125898809</v>
       </c>
       <c r="B18" t="n">
-        <v>57654</v>
+        <v>91265</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,42 +2305,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bobesök?</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Käringtäppan, Käringtäppan, Srm</t>
+          <t>Årby Långkärr, Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616923</v>
+        <v>617125</v>
       </c>
       <c r="R18" t="n">
-        <v>6562795</v>
+        <v>6562956</v>
       </c>
       <c r="S18" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2367,19 +2371,9 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,10 +2400,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125898809</v>
+        <v>125898903</v>
       </c>
       <c r="B19" t="n">
-        <v>91265</v>
+        <v>57654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2417,46 +2411,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Årby Långkärr, Srm</t>
+          <t>Käringtäppan, Käringtäppan, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>617125</v>
+        <v>616923</v>
       </c>
       <c r="R19" t="n">
-        <v>6562956</v>
+        <v>6562795</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2483,9 +2473,19 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4035,10 +4035,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125897142</v>
+        <v>125898732</v>
       </c>
       <c r="B35" t="n">
-        <v>57815</v>
+        <v>57654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4046,16 +4046,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4063,31 +4063,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dammkärr, Dammkärr, Srm</t>
+          <t>Penningdroget, Penningdroget, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>616889</v>
+        <v>617358</v>
       </c>
       <c r="R35" t="n">
-        <v>6562374</v>
+        <v>6562976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4119,7 +4110,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4129,7 +4120,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4156,10 +4147,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125898732</v>
+        <v>125897142</v>
       </c>
       <c r="B36" t="n">
-        <v>57654</v>
+        <v>57815</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4167,16 +4158,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4184,22 +4175,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Penningdroget, Penningdroget, Srm</t>
+          <t>Dammkärr, Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617358</v>
+        <v>616889</v>
       </c>
       <c r="R36" t="n">
-        <v>6562976</v>
+        <v>6562374</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -7481,48 +7481,52 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126384636</v>
+        <v>126443623</v>
       </c>
       <c r="B67" t="n">
-        <v>5176</v>
+        <v>96614</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>617299</v>
+        <v>617291</v>
       </c>
       <c r="R67" t="n">
-        <v>6562881</v>
+        <v>6562787</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7549,19 +7553,14 @@
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:52</t>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På gammal tallåga. Gammal flerskiktad barrsumpskog med inslag av björk och enstaka asp. Inslag av död ved i form av torrträd, högstubbar och gamla lågor av både gran, tall och björk.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7570,28 +7569,29 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Johan Björkstén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johan Björkstén</t>
+          <t>Bo Törnquist, Johan Björkstén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126443868</v>
+        <v>126384636</v>
       </c>
       <c r="B68" t="n">
-        <v>97243</v>
+        <v>5176</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7599,37 +7599,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>224364</v>
+        <v>100526</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>617125</v>
+        <v>617299</v>
       </c>
       <c r="R68" t="n">
-        <v>6562711</v>
+        <v>6562881</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7656,14 +7656,19 @@
           <t>2025-07-03</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Riklig lokal.</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7672,53 +7677,48 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Johan Björkstén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén</t>
+          <t>Johan Björkstén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126443623</v>
+        <v>126443868</v>
       </c>
       <c r="B69" t="n">
-        <v>96614</v>
+        <v>97243</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>53</v>
+        <v>224364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -7730,10 +7730,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>617291</v>
+        <v>617125</v>
       </c>
       <c r="R69" t="n">
-        <v>6562787</v>
+        <v>6562711</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På gammal tallåga. Gammal flerskiktad barrsumpskog med inslag av björk och enstaka asp. Inslag av död ved i form av torrträd, högstubbar och gamla lågor av både gran, tall och björk.</t>
+          <t>Riklig lokal.</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -7481,52 +7481,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126443623</v>
+        <v>126384636</v>
       </c>
       <c r="B67" t="n">
-        <v>96614</v>
+        <v>5176</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>617291</v>
+        <v>617299</v>
       </c>
       <c r="R67" t="n">
-        <v>6562787</v>
+        <v>6562881</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7553,14 +7549,19 @@
           <t>2025-07-03</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På gammal tallåga. Gammal flerskiktad barrsumpskog med inslag av björk och enstaka asp. Inslag av död ved i form av torrträd, högstubbar och gamla lågor av både gran, tall och björk.</t>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7569,29 +7570,28 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Johan Björkstén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén</t>
+          <t>Johan Björkstén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126384636</v>
+        <v>126443868</v>
       </c>
       <c r="B68" t="n">
-        <v>5176</v>
+        <v>97243</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7599,37 +7599,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100526</v>
+        <v>224364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>617299</v>
+        <v>617125</v>
       </c>
       <c r="R68" t="n">
-        <v>6562881</v>
+        <v>6562711</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7656,19 +7656,14 @@
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>12:52</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Riklig lokal.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7677,48 +7672,53 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johan Björkstén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johan Björkstén</t>
+          <t>Bo Törnquist, Johan Björkstén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126443868</v>
+        <v>126443623</v>
       </c>
       <c r="B69" t="n">
-        <v>97243</v>
+        <v>96614</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>224364</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -7730,10 +7730,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>617125</v>
+        <v>617291</v>
       </c>
       <c r="R69" t="n">
-        <v>6562711</v>
+        <v>6562787</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Riklig lokal.</t>
+          <t>På gammal tallåga. Gammal flerskiktad barrsumpskog med inslag av björk och enstaka asp. Inslag av död ved i form av torrträd, högstubbar och gamla lågor av både gran, tall och björk.</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 26357-2025 artfynd.xlsx
+++ b/artfynd/A 26357-2025 artfynd.xlsx
@@ -7481,48 +7481,52 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126384636</v>
+        <v>126443623</v>
       </c>
       <c r="B67" t="n">
-        <v>5176</v>
+        <v>96614</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svartkärret, Svartkärret, Srm</t>
+          <t>Årby Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>617299</v>
+        <v>617291</v>
       </c>
       <c r="R67" t="n">
-        <v>6562881</v>
+        <v>6562787</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7549,19 +7553,14 @@
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:52</t>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På gammal tallåga. Gammal flerskiktad barrsumpskog med inslag av björk och enstaka asp. Inslag av död ved i form av torrträd, högstubbar och gamla lågor av både gran, tall och björk.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7570,28 +7569,29 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Johan Björkstén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johan Björkstén</t>
+          <t>Bo Törnquist, Johan Björkstén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126443868</v>
+        <v>126384636</v>
       </c>
       <c r="B68" t="n">
-        <v>97243</v>
+        <v>5176</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7599,37 +7599,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>224364</v>
+        <v>100526</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Årby Långkärr, Srm</t>
+          <t>Svartkärret, Svartkärret, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>617125</v>
+        <v>617299</v>
       </c>
       <c r="R68" t="n">
-        <v>6562711</v>
+        <v>6562881</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7656,14 +7656,19 @@
           <t>2025-07-03</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Riklig lokal.</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7672,53 +7677,48 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Johan Björkstén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén</t>
+          <t>Johan Björkstén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126443623</v>
+        <v>126443868</v>
       </c>
       <c r="B69" t="n">
-        <v>96614</v>
+        <v>97243</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>53</v>
+        <v>224364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -7730,10 +7730,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>617291</v>
+        <v>617125</v>
       </c>
       <c r="R69" t="n">
-        <v>6562787</v>
+        <v>6562711</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På gammal tallåga. Gammal flerskiktad barrsumpskog med inslag av björk och enstaka asp. Inslag av död ved i form av torrträd, högstubbar och gamla lågor av både gran, tall och björk.</t>
+          <t>Riklig lokal.</t>
         </is>
       </c>
       <c r="AD69" t="b">
